--- a/Docs/InstaMIS.xlsx
+++ b/Docs/InstaMIS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DOWNLOADS\ENERGY_MATRIX_UAT\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DOWNLOADS\energymatrix_uat\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4611E7A-6FEB-40E9-9B9B-BEDC161AE1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE5FB2C-6279-47E6-B385-5BC7895589BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Screens" sheetId="3" r:id="rId1"/>
@@ -20,13 +20,14 @@
     <sheet name="Screen Allotments" sheetId="7" r:id="rId5"/>
     <sheet name="FIRST RELEASE" sheetId="5" r:id="rId6"/>
     <sheet name="Correction(24-03)" sheetId="8" r:id="rId7"/>
+    <sheet name="28-04" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="201">
   <si>
     <t>CHANGES TO BE MADE</t>
   </si>
@@ -662,6 +663,21 @@
   </si>
   <si>
     <t>Only if posted it must come in drop-down</t>
+  </si>
+  <si>
+    <t>Compare daily generation  manual typed and EB statement</t>
+  </si>
+  <si>
+    <t>In master windmill list alise columns to be added and also operator contact number to be visible in main screen</t>
+  </si>
+  <si>
+    <t>display all alise in all where ever needed</t>
+  </si>
+  <si>
+    <t>TNEB plugin to direct download generation statement into the software</t>
+  </si>
+  <si>
+    <t>Texmo  in customer consumption request page in master we made inactive but still showing as active</t>
   </si>
 </sst>
 </file>
@@ -1102,7 +1118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1166,57 +1182,9 @@
     <xf numFmtId="49" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1229,19 +1197,55 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1252,6 +1256,15 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1265,92 +1278,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1373,9 +1308,96 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2518,12 +2540,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.5" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
       <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="15.5" customHeight="1">
@@ -2542,13 +2564,13 @@
       <c r="E2" s="26"/>
     </row>
     <row r="3" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A3" s="39">
+      <c r="A3" s="51">
         <v>1</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D3" s="28" t="s">
@@ -2557,63 +2579,63 @@
       <c r="E3" s="26"/>
     </row>
     <row r="4" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="43"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="46"/>
       <c r="D4" s="28" t="s">
         <v>97</v>
       </c>
       <c r="E4" s="26"/>
     </row>
     <row r="5" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A5" s="40"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="43"/>
+      <c r="A5" s="49"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="46"/>
       <c r="D5" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E5" s="26"/>
     </row>
     <row r="6" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A6" s="40"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="43"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="46"/>
       <c r="D6" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E6" s="26"/>
     </row>
     <row r="7" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A7" s="40"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="43"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="46"/>
       <c r="D7" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E7" s="26"/>
     </row>
     <row r="8" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A8" s="40"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="43"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="46"/>
       <c r="D8" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A9" s="40"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="43"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="46"/>
       <c r="D9" s="28" t="s">
         <v>102</v>
       </c>
       <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A10" s="40"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="42" t="s">
+      <c r="A10" s="49"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D10" s="28" t="s">
@@ -2622,27 +2644,27 @@
       <c r="E10" s="26"/>
     </row>
     <row r="11" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A11" s="40"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="43"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="46"/>
       <c r="D11" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E11" s="26"/>
     </row>
     <row r="12" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A12" s="40"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="43"/>
+      <c r="A12" s="49"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="46"/>
       <c r="D12" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A13" s="40"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="42" t="s">
+      <c r="A13" s="49"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D13" s="28" t="s">
@@ -2651,31 +2673,31 @@
       <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A14" s="40"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="43"/>
+      <c r="A14" s="49"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="46"/>
       <c r="D14" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E14" s="26"/>
     </row>
     <row r="15" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A15" s="40"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="43"/>
+      <c r="A15" s="49"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="46"/>
       <c r="D15" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E15" s="26"/>
     </row>
     <row r="16" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A16" s="39">
+      <c r="A16" s="51">
         <v>2</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D16" s="28" t="s">
@@ -2684,63 +2706,63 @@
       <c r="E16" s="26"/>
     </row>
     <row r="17" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A17" s="40"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="43"/>
+      <c r="A17" s="49"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="46"/>
       <c r="D17" s="28" t="s">
         <v>97</v>
       </c>
       <c r="E17" s="26"/>
     </row>
     <row r="18" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="43"/>
+      <c r="A18" s="49"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="46"/>
       <c r="D18" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E18" s="26"/>
     </row>
     <row r="19" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="43"/>
+      <c r="A19" s="49"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="46"/>
       <c r="D19" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E19" s="26"/>
     </row>
     <row r="20" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="43"/>
+      <c r="A20" s="49"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="46"/>
       <c r="D20" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E20" s="26"/>
     </row>
     <row r="21" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="43"/>
+      <c r="A21" s="49"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="46"/>
       <c r="D21" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E21" s="26"/>
     </row>
     <row r="22" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="43"/>
+      <c r="A22" s="49"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="46"/>
       <c r="D22" s="28" t="s">
         <v>102</v>
       </c>
       <c r="E22" s="26"/>
     </row>
     <row r="23" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="42" t="s">
+      <c r="A23" s="49"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D23" s="28" t="s">
@@ -2749,27 +2771,27 @@
       <c r="E23" s="26"/>
     </row>
     <row r="24" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A24" s="40"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="43"/>
+      <c r="A24" s="49"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="46"/>
       <c r="D24" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E24" s="26"/>
     </row>
     <row r="25" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A25" s="40"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="43"/>
+      <c r="A25" s="49"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="46"/>
       <c r="D25" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E25" s="26"/>
     </row>
     <row r="26" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A26" s="40"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="42" t="s">
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D26" s="28" t="s">
@@ -2778,31 +2800,31 @@
       <c r="E26" s="26"/>
     </row>
     <row r="27" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A27" s="40"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="43"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="46"/>
       <c r="D27" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E27" s="26"/>
     </row>
     <row r="28" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A28" s="40"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="43"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="46"/>
       <c r="D28" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E28" s="26"/>
     </row>
     <row r="29" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A29" s="44">
+      <c r="A29" s="52">
         <v>3</v>
       </c>
-      <c r="B29" s="46" t="s">
+      <c r="B29" s="54" t="s">
         <v>166</v>
       </c>
-      <c r="C29" s="42" t="s">
+      <c r="C29" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D29" s="28" t="s">
@@ -2811,63 +2833,63 @@
       <c r="E29" s="26"/>
     </row>
     <row r="30" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="43"/>
+      <c r="A30" s="53"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="46"/>
       <c r="D30" s="28" t="s">
         <v>97</v>
       </c>
       <c r="E30" s="26"/>
     </row>
     <row r="31" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A31" s="45"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="43"/>
+      <c r="A31" s="53"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="46"/>
       <c r="D31" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E31" s="26"/>
     </row>
     <row r="32" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A32" s="45"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="43"/>
+      <c r="A32" s="53"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="46"/>
       <c r="D32" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A33" s="45"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="43"/>
+      <c r="A33" s="53"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="46"/>
       <c r="D33" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E33" s="26"/>
     </row>
     <row r="34" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A34" s="45"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="43"/>
+      <c r="A34" s="53"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="46"/>
       <c r="D34" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E34" s="26"/>
     </row>
     <row r="35" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A35" s="45"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="43"/>
+      <c r="A35" s="53"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="46"/>
       <c r="D35" s="28" t="s">
         <v>102</v>
       </c>
       <c r="E35" s="26"/>
     </row>
     <row r="36" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A36" s="45"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="42" t="s">
+      <c r="A36" s="53"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D36" s="28" t="s">
@@ -2876,27 +2898,27 @@
       <c r="E36" s="26"/>
     </row>
     <row r="37" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A37" s="45"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="43"/>
+      <c r="A37" s="53"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="46"/>
       <c r="D37" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E37" s="26"/>
     </row>
     <row r="38" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A38" s="45"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="43"/>
+      <c r="A38" s="53"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="46"/>
       <c r="D38" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E38" s="26"/>
     </row>
     <row r="39" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A39" s="45"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="42" t="s">
+      <c r="A39" s="53"/>
+      <c r="B39" s="53"/>
+      <c r="C39" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D39" s="28" t="s">
@@ -2905,59 +2927,59 @@
       <c r="E39" s="26"/>
     </row>
     <row r="40" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A40" s="45"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="43"/>
+      <c r="A40" s="53"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="46"/>
       <c r="D40" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E40" s="26"/>
     </row>
     <row r="41" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A41" s="45"/>
-      <c r="B41" s="45"/>
-      <c r="C41" s="43"/>
+      <c r="A41" s="53"/>
+      <c r="B41" s="53"/>
+      <c r="C41" s="46"/>
       <c r="D41" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E41" s="26"/>
     </row>
     <row r="42" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A42" s="45"/>
-      <c r="B42" s="45"/>
+      <c r="A42" s="53"/>
+      <c r="B42" s="53"/>
       <c r="C42" s="29"/>
       <c r="D42" s="30"/>
       <c r="E42" s="26"/>
     </row>
     <row r="43" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A43" s="45"/>
-      <c r="B43" s="45"/>
+      <c r="A43" s="53"/>
+      <c r="B43" s="53"/>
       <c r="C43" s="29"/>
       <c r="D43" s="30"/>
       <c r="E43" s="26"/>
     </row>
     <row r="44" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A44" s="45"/>
-      <c r="B44" s="45"/>
+      <c r="A44" s="53"/>
+      <c r="B44" s="53"/>
       <c r="C44" s="29"/>
       <c r="D44" s="30"/>
       <c r="E44" s="26"/>
     </row>
     <row r="45" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A45" s="45"/>
-      <c r="B45" s="45"/>
+      <c r="A45" s="53"/>
+      <c r="B45" s="53"/>
       <c r="C45" s="29"/>
       <c r="D45" s="30"/>
       <c r="E45" s="26"/>
     </row>
     <row r="46" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A46" s="39">
+      <c r="A46" s="51">
         <v>4</v>
       </c>
-      <c r="B46" s="41" t="s">
+      <c r="B46" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="C46" s="42" t="s">
+      <c r="C46" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D46" s="28" t="s">
@@ -2966,63 +2988,63 @@
       <c r="E46" s="26"/>
     </row>
     <row r="47" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A47" s="40"/>
-      <c r="B47" s="40"/>
-      <c r="C47" s="43"/>
+      <c r="A47" s="49"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="46"/>
       <c r="D47" s="28" t="s">
         <v>97</v>
       </c>
       <c r="E47" s="26"/>
     </row>
     <row r="48" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A48" s="40"/>
-      <c r="B48" s="40"/>
-      <c r="C48" s="43"/>
+      <c r="A48" s="49"/>
+      <c r="B48" s="49"/>
+      <c r="C48" s="46"/>
       <c r="D48" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E48" s="26"/>
     </row>
     <row r="49" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A49" s="40"/>
-      <c r="B49" s="40"/>
-      <c r="C49" s="43"/>
+      <c r="A49" s="49"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="46"/>
       <c r="D49" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E49" s="26"/>
     </row>
     <row r="50" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A50" s="40"/>
-      <c r="B50" s="40"/>
-      <c r="C50" s="43"/>
+      <c r="A50" s="49"/>
+      <c r="B50" s="49"/>
+      <c r="C50" s="46"/>
       <c r="D50" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E50" s="26"/>
     </row>
     <row r="51" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A51" s="40"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="43"/>
+      <c r="A51" s="49"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="46"/>
       <c r="D51" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E51" s="26"/>
     </row>
     <row r="52" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A52" s="40"/>
-      <c r="B52" s="40"/>
-      <c r="C52" s="43"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="49"/>
+      <c r="C52" s="46"/>
       <c r="D52" s="28" t="s">
         <v>102</v>
       </c>
       <c r="E52" s="26"/>
     </row>
     <row r="53" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A53" s="40"/>
-      <c r="B53" s="40"/>
-      <c r="C53" s="42" t="s">
+      <c r="A53" s="49"/>
+      <c r="B53" s="49"/>
+      <c r="C53" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D53" s="28" t="s">
@@ -3031,45 +3053,45 @@
       <c r="E53" s="26"/>
     </row>
     <row r="54" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A54" s="40"/>
-      <c r="B54" s="40"/>
-      <c r="C54" s="43"/>
+      <c r="A54" s="49"/>
+      <c r="B54" s="49"/>
+      <c r="C54" s="46"/>
       <c r="D54" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E54" s="26"/>
     </row>
     <row r="55" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A55" s="40"/>
-      <c r="B55" s="40"/>
-      <c r="C55" s="43"/>
+      <c r="A55" s="49"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="46"/>
       <c r="D55" s="28" t="s">
         <v>106</v>
       </c>
       <c r="E55" s="26"/>
     </row>
     <row r="56" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A56" s="40"/>
-      <c r="B56" s="40"/>
-      <c r="C56" s="43"/>
+      <c r="A56" s="49"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="46"/>
       <c r="D56" s="28" t="s">
         <v>107</v>
       </c>
       <c r="E56" s="26"/>
     </row>
     <row r="57" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A57" s="40"/>
-      <c r="B57" s="40"/>
-      <c r="C57" s="43"/>
+      <c r="A57" s="49"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="46"/>
       <c r="D57" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E57" s="26"/>
     </row>
     <row r="58" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A58" s="40"/>
-      <c r="B58" s="40"/>
-      <c r="C58" s="42" t="s">
+      <c r="A58" s="49"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D58" s="28" t="s">
@@ -3078,49 +3100,49 @@
       <c r="E58" s="26"/>
     </row>
     <row r="59" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A59" s="40"/>
-      <c r="B59" s="40"/>
-      <c r="C59" s="43"/>
+      <c r="A59" s="49"/>
+      <c r="B59" s="49"/>
+      <c r="C59" s="46"/>
       <c r="D59" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E59" s="26"/>
     </row>
     <row r="60" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A60" s="40"/>
-      <c r="B60" s="40"/>
-      <c r="C60" s="43"/>
+      <c r="A60" s="49"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="46"/>
       <c r="D60" s="28" t="s">
         <v>106</v>
       </c>
       <c r="E60" s="26"/>
     </row>
     <row r="61" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A61" s="40"/>
-      <c r="B61" s="40"/>
-      <c r="C61" s="43"/>
+      <c r="A61" s="49"/>
+      <c r="B61" s="49"/>
+      <c r="C61" s="46"/>
       <c r="D61" s="28" t="s">
         <v>107</v>
       </c>
       <c r="E61" s="26"/>
     </row>
     <row r="62" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A62" s="40"/>
-      <c r="B62" s="40"/>
-      <c r="C62" s="43"/>
+      <c r="A62" s="49"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="46"/>
       <c r="D62" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E62" s="26"/>
     </row>
     <row r="63" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A63" s="39">
+      <c r="A63" s="51">
         <v>5</v>
       </c>
-      <c r="B63" s="41" t="s">
+      <c r="B63" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="C63" s="42" t="s">
+      <c r="C63" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D63" s="28" t="s">
@@ -3129,63 +3151,63 @@
       <c r="E63" s="26"/>
     </row>
     <row r="64" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A64" s="40"/>
-      <c r="B64" s="40"/>
-      <c r="C64" s="43"/>
+      <c r="A64" s="49"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="46"/>
       <c r="D64" s="28" t="s">
         <v>97</v>
       </c>
       <c r="E64" s="26"/>
     </row>
     <row r="65" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A65" s="40"/>
-      <c r="B65" s="40"/>
-      <c r="C65" s="43"/>
+      <c r="A65" s="49"/>
+      <c r="B65" s="49"/>
+      <c r="C65" s="46"/>
       <c r="D65" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E65" s="26"/>
     </row>
     <row r="66" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A66" s="40"/>
-      <c r="B66" s="40"/>
-      <c r="C66" s="43"/>
+      <c r="A66" s="49"/>
+      <c r="B66" s="49"/>
+      <c r="C66" s="46"/>
       <c r="D66" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E66" s="26"/>
     </row>
     <row r="67" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A67" s="40"/>
-      <c r="B67" s="40"/>
-      <c r="C67" s="43"/>
+      <c r="A67" s="49"/>
+      <c r="B67" s="49"/>
+      <c r="C67" s="46"/>
       <c r="D67" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E67" s="26"/>
     </row>
     <row r="68" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A68" s="40"/>
-      <c r="B68" s="40"/>
-      <c r="C68" s="43"/>
+      <c r="A68" s="49"/>
+      <c r="B68" s="49"/>
+      <c r="C68" s="46"/>
       <c r="D68" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E68" s="26"/>
     </row>
     <row r="69" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A69" s="40"/>
-      <c r="B69" s="40"/>
-      <c r="C69" s="43"/>
+      <c r="A69" s="49"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="46"/>
       <c r="D69" s="28" t="s">
         <v>102</v>
       </c>
       <c r="E69" s="26"/>
     </row>
     <row r="70" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A70" s="40"/>
-      <c r="B70" s="40"/>
-      <c r="C70" s="42" t="s">
+      <c r="A70" s="49"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D70" s="28" t="s">
@@ -3194,72 +3216,72 @@
       <c r="E70" s="26"/>
     </row>
     <row r="71" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A71" s="40"/>
-      <c r="B71" s="40"/>
-      <c r="C71" s="43"/>
+      <c r="A71" s="49"/>
+      <c r="B71" s="49"/>
+      <c r="C71" s="46"/>
       <c r="D71" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E71" s="26"/>
     </row>
     <row r="72" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A72" s="40"/>
-      <c r="B72" s="40"/>
-      <c r="C72" s="43"/>
+      <c r="A72" s="49"/>
+      <c r="B72" s="49"/>
+      <c r="C72" s="46"/>
       <c r="D72" s="28" t="s">
         <v>41</v>
       </c>
       <c r="E72" s="26"/>
     </row>
     <row r="73" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A73" s="40"/>
-      <c r="B73" s="40"/>
-      <c r="C73" s="43"/>
+      <c r="A73" s="49"/>
+      <c r="B73" s="49"/>
+      <c r="C73" s="46"/>
       <c r="D73" s="28" t="s">
         <v>109</v>
       </c>
       <c r="E73" s="26"/>
     </row>
     <row r="74" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A74" s="40"/>
-      <c r="B74" s="40"/>
-      <c r="C74" s="43"/>
+      <c r="A74" s="49"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="46"/>
       <c r="D74" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E74" s="26"/>
     </row>
     <row r="75" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A75" s="40"/>
-      <c r="B75" s="40"/>
-      <c r="C75" s="43"/>
+      <c r="A75" s="49"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="46"/>
       <c r="D75" s="28" t="s">
         <v>111</v>
       </c>
       <c r="E75" s="26"/>
     </row>
     <row r="76" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A76" s="40"/>
-      <c r="B76" s="40"/>
-      <c r="C76" s="43"/>
+      <c r="A76" s="49"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="46"/>
       <c r="D76" s="28" t="s">
         <v>112</v>
       </c>
       <c r="E76" s="26"/>
     </row>
     <row r="77" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A77" s="40"/>
-      <c r="B77" s="40"/>
-      <c r="C77" s="43"/>
+      <c r="A77" s="49"/>
+      <c r="B77" s="49"/>
+      <c r="C77" s="46"/>
       <c r="D77" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E77" s="26"/>
     </row>
     <row r="78" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A78" s="40"/>
-      <c r="B78" s="40"/>
-      <c r="C78" s="42" t="s">
+      <c r="A78" s="49"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D78" s="28" t="s">
@@ -3268,76 +3290,76 @@
       <c r="E78" s="26"/>
     </row>
     <row r="79" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A79" s="40"/>
-      <c r="B79" s="40"/>
-      <c r="C79" s="43"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="46"/>
       <c r="D79" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E79" s="26"/>
     </row>
     <row r="80" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A80" s="40"/>
-      <c r="B80" s="40"/>
-      <c r="C80" s="43"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="46"/>
       <c r="D80" s="28" t="s">
         <v>41</v>
       </c>
       <c r="E80" s="26"/>
     </row>
     <row r="81" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A81" s="40"/>
-      <c r="B81" s="40"/>
-      <c r="C81" s="43"/>
+      <c r="A81" s="49"/>
+      <c r="B81" s="49"/>
+      <c r="C81" s="46"/>
       <c r="D81" s="28" t="s">
         <v>109</v>
       </c>
       <c r="E81" s="26"/>
     </row>
     <row r="82" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A82" s="40"/>
-      <c r="B82" s="40"/>
-      <c r="C82" s="43"/>
+      <c r="A82" s="49"/>
+      <c r="B82" s="49"/>
+      <c r="C82" s="46"/>
       <c r="D82" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E82" s="26"/>
     </row>
     <row r="83" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A83" s="40"/>
-      <c r="B83" s="40"/>
-      <c r="C83" s="43"/>
+      <c r="A83" s="49"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="46"/>
       <c r="D83" s="28" t="s">
         <v>111</v>
       </c>
       <c r="E83" s="26"/>
     </row>
     <row r="84" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A84" s="40"/>
-      <c r="B84" s="40"/>
-      <c r="C84" s="43"/>
+      <c r="A84" s="49"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="46"/>
       <c r="D84" s="28" t="s">
         <v>112</v>
       </c>
       <c r="E84" s="26"/>
     </row>
     <row r="85" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A85" s="40"/>
-      <c r="B85" s="40"/>
-      <c r="C85" s="43"/>
+      <c r="A85" s="49"/>
+      <c r="B85" s="49"/>
+      <c r="C85" s="46"/>
       <c r="D85" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E85" s="26"/>
     </row>
     <row r="86" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A86" s="39">
+      <c r="A86" s="51">
         <v>6</v>
       </c>
-      <c r="B86" s="41" t="s">
+      <c r="B86" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="C86" s="42" t="s">
+      <c r="C86" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D86" s="28" t="s">
@@ -3346,63 +3368,63 @@
       <c r="E86" s="26"/>
     </row>
     <row r="87" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A87" s="40"/>
-      <c r="B87" s="40"/>
-      <c r="C87" s="43"/>
+      <c r="A87" s="49"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="46"/>
       <c r="D87" s="28" t="s">
         <v>97</v>
       </c>
       <c r="E87" s="26"/>
     </row>
     <row r="88" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A88" s="40"/>
-      <c r="B88" s="40"/>
-      <c r="C88" s="43"/>
+      <c r="A88" s="49"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="46"/>
       <c r="D88" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E88" s="26"/>
     </row>
     <row r="89" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A89" s="40"/>
-      <c r="B89" s="40"/>
-      <c r="C89" s="43"/>
+      <c r="A89" s="49"/>
+      <c r="B89" s="49"/>
+      <c r="C89" s="46"/>
       <c r="D89" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E89" s="26"/>
     </row>
     <row r="90" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A90" s="40"/>
-      <c r="B90" s="40"/>
-      <c r="C90" s="43"/>
+      <c r="A90" s="49"/>
+      <c r="B90" s="49"/>
+      <c r="C90" s="46"/>
       <c r="D90" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E90" s="26"/>
     </row>
     <row r="91" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A91" s="40"/>
-      <c r="B91" s="40"/>
-      <c r="C91" s="43"/>
+      <c r="A91" s="49"/>
+      <c r="B91" s="49"/>
+      <c r="C91" s="46"/>
       <c r="D91" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E91" s="26"/>
     </row>
     <row r="92" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A92" s="40"/>
-      <c r="B92" s="40"/>
-      <c r="C92" s="43"/>
+      <c r="A92" s="49"/>
+      <c r="B92" s="49"/>
+      <c r="C92" s="46"/>
       <c r="D92" s="28" t="s">
         <v>102</v>
       </c>
       <c r="E92" s="26"/>
     </row>
     <row r="93" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A93" s="40"/>
-      <c r="B93" s="40"/>
-      <c r="C93" s="42" t="s">
+      <c r="A93" s="49"/>
+      <c r="B93" s="49"/>
+      <c r="C93" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D93" s="28" t="s">
@@ -3411,27 +3433,27 @@
       <c r="E93" s="26"/>
     </row>
     <row r="94" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A94" s="40"/>
-      <c r="B94" s="40"/>
-      <c r="C94" s="43"/>
+      <c r="A94" s="49"/>
+      <c r="B94" s="49"/>
+      <c r="C94" s="46"/>
       <c r="D94" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E94" s="26"/>
     </row>
     <row r="95" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A95" s="40"/>
-      <c r="B95" s="40"/>
-      <c r="C95" s="43"/>
+      <c r="A95" s="49"/>
+      <c r="B95" s="49"/>
+      <c r="C95" s="46"/>
       <c r="D95" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E95" s="26"/>
     </row>
     <row r="96" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A96" s="40"/>
-      <c r="B96" s="40"/>
-      <c r="C96" s="42" t="s">
+      <c r="A96" s="49"/>
+      <c r="B96" s="49"/>
+      <c r="C96" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D96" s="28" t="s">
@@ -3440,31 +3462,31 @@
       <c r="E96" s="26"/>
     </row>
     <row r="97" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A97" s="40"/>
-      <c r="B97" s="40"/>
-      <c r="C97" s="43"/>
+      <c r="A97" s="49"/>
+      <c r="B97" s="49"/>
+      <c r="C97" s="46"/>
       <c r="D97" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E97" s="26"/>
     </row>
     <row r="98" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A98" s="40"/>
-      <c r="B98" s="40"/>
-      <c r="C98" s="43"/>
+      <c r="A98" s="49"/>
+      <c r="B98" s="49"/>
+      <c r="C98" s="46"/>
       <c r="D98" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E98" s="26"/>
     </row>
     <row r="99" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A99" s="39">
+      <c r="A99" s="51">
         <v>7</v>
       </c>
-      <c r="B99" s="41" t="s">
+      <c r="B99" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="C99" s="42" t="s">
+      <c r="C99" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D99" s="28" t="s">
@@ -3473,63 +3495,63 @@
       <c r="E99" s="26"/>
     </row>
     <row r="100" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A100" s="40"/>
-      <c r="B100" s="40"/>
-      <c r="C100" s="43"/>
+      <c r="A100" s="49"/>
+      <c r="B100" s="49"/>
+      <c r="C100" s="46"/>
       <c r="D100" s="28" t="s">
         <v>97</v>
       </c>
       <c r="E100" s="26"/>
     </row>
     <row r="101" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A101" s="40"/>
-      <c r="B101" s="40"/>
-      <c r="C101" s="43"/>
+      <c r="A101" s="49"/>
+      <c r="B101" s="49"/>
+      <c r="C101" s="46"/>
       <c r="D101" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E101" s="26"/>
     </row>
     <row r="102" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A102" s="40"/>
-      <c r="B102" s="40"/>
-      <c r="C102" s="43"/>
+      <c r="A102" s="49"/>
+      <c r="B102" s="49"/>
+      <c r="C102" s="46"/>
       <c r="D102" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E102" s="26"/>
     </row>
     <row r="103" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A103" s="40"/>
-      <c r="B103" s="40"/>
-      <c r="C103" s="43"/>
+      <c r="A103" s="49"/>
+      <c r="B103" s="49"/>
+      <c r="C103" s="46"/>
       <c r="D103" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E103" s="26"/>
     </row>
     <row r="104" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A104" s="40"/>
-      <c r="B104" s="40"/>
-      <c r="C104" s="43"/>
+      <c r="A104" s="49"/>
+      <c r="B104" s="49"/>
+      <c r="C104" s="46"/>
       <c r="D104" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E104" s="26"/>
     </row>
     <row r="105" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A105" s="40"/>
-      <c r="B105" s="40"/>
-      <c r="C105" s="43"/>
+      <c r="A105" s="49"/>
+      <c r="B105" s="49"/>
+      <c r="C105" s="46"/>
       <c r="D105" s="28" t="s">
         <v>102</v>
       </c>
       <c r="E105" s="26"/>
     </row>
     <row r="106" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A106" s="40"/>
-      <c r="B106" s="40"/>
-      <c r="C106" s="42" t="s">
+      <c r="A106" s="49"/>
+      <c r="B106" s="49"/>
+      <c r="C106" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D106" s="28" t="s">
@@ -3538,27 +3560,27 @@
       <c r="E106" s="26"/>
     </row>
     <row r="107" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A107" s="40"/>
-      <c r="B107" s="40"/>
-      <c r="C107" s="43"/>
+      <c r="A107" s="49"/>
+      <c r="B107" s="49"/>
+      <c r="C107" s="46"/>
       <c r="D107" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E107" s="26"/>
     </row>
     <row r="108" spans="1:5" ht="15" customHeight="1">
-      <c r="A108" s="40"/>
-      <c r="B108" s="40"/>
-      <c r="C108" s="43"/>
+      <c r="A108" s="49"/>
+      <c r="B108" s="49"/>
+      <c r="C108" s="46"/>
       <c r="D108" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E108" s="26"/>
     </row>
     <row r="109" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A109" s="40"/>
-      <c r="B109" s="40"/>
-      <c r="C109" s="42" t="s">
+      <c r="A109" s="49"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D109" s="28" t="s">
@@ -3567,31 +3589,31 @@
       <c r="E109" s="26"/>
     </row>
     <row r="110" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A110" s="40"/>
-      <c r="B110" s="40"/>
-      <c r="C110" s="43"/>
+      <c r="A110" s="49"/>
+      <c r="B110" s="49"/>
+      <c r="C110" s="46"/>
       <c r="D110" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E110" s="26"/>
     </row>
     <row r="111" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A111" s="40"/>
-      <c r="B111" s="40"/>
-      <c r="C111" s="43"/>
+      <c r="A111" s="49"/>
+      <c r="B111" s="49"/>
+      <c r="C111" s="46"/>
       <c r="D111" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E111" s="26"/>
     </row>
     <row r="112" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A112" s="39">
+      <c r="A112" s="51">
         <v>8</v>
       </c>
-      <c r="B112" s="41" t="s">
+      <c r="B112" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="C112" s="42" t="s">
+      <c r="C112" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D112" s="28" t="s">
@@ -3600,63 +3622,63 @@
       <c r="E112" s="26"/>
     </row>
     <row r="113" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A113" s="40"/>
-      <c r="B113" s="40"/>
-      <c r="C113" s="43"/>
+      <c r="A113" s="49"/>
+      <c r="B113" s="49"/>
+      <c r="C113" s="46"/>
       <c r="D113" s="28" t="s">
         <v>97</v>
       </c>
       <c r="E113" s="26"/>
     </row>
     <row r="114" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A114" s="40"/>
-      <c r="B114" s="40"/>
-      <c r="C114" s="43"/>
+      <c r="A114" s="49"/>
+      <c r="B114" s="49"/>
+      <c r="C114" s="46"/>
       <c r="D114" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E114" s="26"/>
     </row>
     <row r="115" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A115" s="40"/>
-      <c r="B115" s="40"/>
-      <c r="C115" s="43"/>
+      <c r="A115" s="49"/>
+      <c r="B115" s="49"/>
+      <c r="C115" s="46"/>
       <c r="D115" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E115" s="26"/>
     </row>
     <row r="116" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A116" s="40"/>
-      <c r="B116" s="40"/>
-      <c r="C116" s="43"/>
+      <c r="A116" s="49"/>
+      <c r="B116" s="49"/>
+      <c r="C116" s="46"/>
       <c r="D116" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E116" s="26"/>
     </row>
     <row r="117" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A117" s="40"/>
-      <c r="B117" s="40"/>
-      <c r="C117" s="43"/>
+      <c r="A117" s="49"/>
+      <c r="B117" s="49"/>
+      <c r="C117" s="46"/>
       <c r="D117" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E117" s="26"/>
     </row>
     <row r="118" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A118" s="40"/>
-      <c r="B118" s="40"/>
-      <c r="C118" s="43"/>
+      <c r="A118" s="49"/>
+      <c r="B118" s="49"/>
+      <c r="C118" s="46"/>
       <c r="D118" s="28" t="s">
         <v>102</v>
       </c>
       <c r="E118" s="26"/>
     </row>
     <row r="119" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A119" s="40"/>
-      <c r="B119" s="40"/>
-      <c r="C119" s="42" t="s">
+      <c r="A119" s="49"/>
+      <c r="B119" s="49"/>
+      <c r="C119" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D119" s="28" t="s">
@@ -3665,27 +3687,27 @@
       <c r="E119" s="26"/>
     </row>
     <row r="120" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A120" s="40"/>
-      <c r="B120" s="40"/>
-      <c r="C120" s="43"/>
+      <c r="A120" s="49"/>
+      <c r="B120" s="49"/>
+      <c r="C120" s="46"/>
       <c r="D120" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E120" s="26"/>
     </row>
     <row r="121" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A121" s="40"/>
-      <c r="B121" s="40"/>
-      <c r="C121" s="43"/>
+      <c r="A121" s="49"/>
+      <c r="B121" s="49"/>
+      <c r="C121" s="46"/>
       <c r="D121" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E121" s="26"/>
     </row>
     <row r="122" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A122" s="40"/>
-      <c r="B122" s="40"/>
-      <c r="C122" s="42" t="s">
+      <c r="A122" s="49"/>
+      <c r="B122" s="49"/>
+      <c r="C122" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D122" s="28" t="s">
@@ -3694,31 +3716,31 @@
       <c r="E122" s="26"/>
     </row>
     <row r="123" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A123" s="40"/>
-      <c r="B123" s="40"/>
-      <c r="C123" s="43"/>
+      <c r="A123" s="49"/>
+      <c r="B123" s="49"/>
+      <c r="C123" s="46"/>
       <c r="D123" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E123" s="26"/>
     </row>
     <row r="124" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A124" s="40"/>
-      <c r="B124" s="40"/>
-      <c r="C124" s="43"/>
+      <c r="A124" s="49"/>
+      <c r="B124" s="49"/>
+      <c r="C124" s="46"/>
       <c r="D124" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E124" s="26"/>
     </row>
     <row r="125" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A125" s="39">
+      <c r="A125" s="51">
         <v>9</v>
       </c>
-      <c r="B125" s="41" t="s">
+      <c r="B125" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="C125" s="42" t="s">
+      <c r="C125" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D125" s="28" t="s">
@@ -3727,63 +3749,63 @@
       <c r="E125" s="26"/>
     </row>
     <row r="126" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A126" s="40"/>
-      <c r="B126" s="47"/>
-      <c r="C126" s="43"/>
+      <c r="A126" s="49"/>
+      <c r="B126" s="43"/>
+      <c r="C126" s="46"/>
       <c r="D126" s="28" t="s">
         <v>97</v>
       </c>
       <c r="E126" s="26"/>
     </row>
     <row r="127" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A127" s="40"/>
-      <c r="B127" s="47"/>
-      <c r="C127" s="43"/>
+      <c r="A127" s="49"/>
+      <c r="B127" s="43"/>
+      <c r="C127" s="46"/>
       <c r="D127" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E127" s="26"/>
     </row>
     <row r="128" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A128" s="40"/>
-      <c r="B128" s="47"/>
-      <c r="C128" s="43"/>
+      <c r="A128" s="49"/>
+      <c r="B128" s="43"/>
+      <c r="C128" s="46"/>
       <c r="D128" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E128" s="26"/>
     </row>
     <row r="129" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A129" s="40"/>
-      <c r="B129" s="47"/>
-      <c r="C129" s="43"/>
+      <c r="A129" s="49"/>
+      <c r="B129" s="43"/>
+      <c r="C129" s="46"/>
       <c r="D129" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E129" s="26"/>
     </row>
     <row r="130" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A130" s="40"/>
-      <c r="B130" s="47"/>
-      <c r="C130" s="43"/>
+      <c r="A130" s="49"/>
+      <c r="B130" s="43"/>
+      <c r="C130" s="46"/>
       <c r="D130" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E130" s="26"/>
     </row>
     <row r="131" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A131" s="40"/>
-      <c r="B131" s="47"/>
-      <c r="C131" s="43"/>
+      <c r="A131" s="49"/>
+      <c r="B131" s="43"/>
+      <c r="C131" s="46"/>
       <c r="D131" s="28" t="s">
         <v>102</v>
       </c>
       <c r="E131" s="26"/>
     </row>
     <row r="132" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A132" s="40"/>
-      <c r="B132" s="47"/>
-      <c r="C132" s="42" t="s">
+      <c r="A132" s="49"/>
+      <c r="B132" s="43"/>
+      <c r="C132" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D132" s="28" t="s">
@@ -3792,27 +3814,27 @@
       <c r="E132" s="26"/>
     </row>
     <row r="133" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A133" s="40"/>
-      <c r="B133" s="47"/>
-      <c r="C133" s="43"/>
+      <c r="A133" s="49"/>
+      <c r="B133" s="43"/>
+      <c r="C133" s="46"/>
       <c r="D133" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E133" s="26"/>
     </row>
     <row r="134" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A134" s="40"/>
-      <c r="B134" s="47"/>
-      <c r="C134" s="43"/>
+      <c r="A134" s="49"/>
+      <c r="B134" s="43"/>
+      <c r="C134" s="46"/>
       <c r="D134" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E134" s="26"/>
     </row>
     <row r="135" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A135" s="40"/>
-      <c r="B135" s="47"/>
-      <c r="C135" s="42" t="s">
+      <c r="A135" s="49"/>
+      <c r="B135" s="43"/>
+      <c r="C135" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D135" s="28" t="s">
@@ -3821,30 +3843,30 @@
       <c r="E135" s="26"/>
     </row>
     <row r="136" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A136" s="40"/>
-      <c r="B136" s="47"/>
-      <c r="C136" s="43"/>
+      <c r="A136" s="49"/>
+      <c r="B136" s="43"/>
+      <c r="C136" s="46"/>
       <c r="D136" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E136" s="26"/>
     </row>
     <row r="137" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A137" s="40"/>
-      <c r="B137" s="47"/>
-      <c r="C137" s="43"/>
+      <c r="A137" s="49"/>
+      <c r="B137" s="43"/>
+      <c r="C137" s="46"/>
       <c r="D137" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E137" s="26"/>
     </row>
     <row r="138" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A138" s="48" t="s">
+      <c r="A138" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="B138" s="49"/>
-      <c r="C138" s="49"/>
-      <c r="D138" s="49"/>
+      <c r="B138" s="48"/>
+      <c r="C138" s="48"/>
+      <c r="D138" s="48"/>
       <c r="E138" s="26"/>
     </row>
     <row r="139" spans="1:5" ht="15.5" customHeight="1">
@@ -3874,13 +3896,13 @@
       <c r="E140" s="26"/>
     </row>
     <row r="141" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A141" s="50" t="s">
+      <c r="A141" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="B141" s="41" t="s">
+      <c r="B141" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="C141" s="42" t="s">
+      <c r="C141" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D141" s="28" t="s">
@@ -3889,63 +3911,63 @@
       <c r="E141" s="26"/>
     </row>
     <row r="142" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A142" s="47"/>
-      <c r="B142" s="40"/>
-      <c r="C142" s="43"/>
+      <c r="A142" s="43"/>
+      <c r="B142" s="49"/>
+      <c r="C142" s="46"/>
       <c r="D142" s="28" t="s">
         <v>97</v>
       </c>
       <c r="E142" s="26"/>
     </row>
     <row r="143" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A143" s="47"/>
-      <c r="B143" s="40"/>
-      <c r="C143" s="43"/>
+      <c r="A143" s="43"/>
+      <c r="B143" s="49"/>
+      <c r="C143" s="46"/>
       <c r="D143" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E143" s="26"/>
     </row>
     <row r="144" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A144" s="47"/>
-      <c r="B144" s="40"/>
-      <c r="C144" s="43"/>
+      <c r="A144" s="43"/>
+      <c r="B144" s="49"/>
+      <c r="C144" s="46"/>
       <c r="D144" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E144" s="26"/>
     </row>
     <row r="145" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A145" s="47"/>
-      <c r="B145" s="40"/>
-      <c r="C145" s="43"/>
+      <c r="A145" s="43"/>
+      <c r="B145" s="49"/>
+      <c r="C145" s="46"/>
       <c r="D145" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E145" s="26"/>
     </row>
     <row r="146" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A146" s="47"/>
-      <c r="B146" s="40"/>
-      <c r="C146" s="43"/>
+      <c r="A146" s="43"/>
+      <c r="B146" s="49"/>
+      <c r="C146" s="46"/>
       <c r="D146" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E146" s="26"/>
     </row>
     <row r="147" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A147" s="47"/>
-      <c r="B147" s="40"/>
-      <c r="C147" s="43"/>
+      <c r="A147" s="43"/>
+      <c r="B147" s="49"/>
+      <c r="C147" s="46"/>
       <c r="D147" s="28" t="s">
         <v>102</v>
       </c>
       <c r="E147" s="26"/>
     </row>
     <row r="148" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A148" s="47"/>
-      <c r="B148" s="40"/>
-      <c r="C148" s="42" t="s">
+      <c r="A148" s="43"/>
+      <c r="B148" s="49"/>
+      <c r="C148" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D148" s="28" t="s">
@@ -3954,27 +3976,27 @@
       <c r="E148" s="26"/>
     </row>
     <row r="149" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A149" s="47"/>
-      <c r="B149" s="40"/>
-      <c r="C149" s="43"/>
+      <c r="A149" s="43"/>
+      <c r="B149" s="49"/>
+      <c r="C149" s="46"/>
       <c r="D149" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E149" s="26"/>
     </row>
     <row r="150" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A150" s="47"/>
-      <c r="B150" s="40"/>
-      <c r="C150" s="43"/>
+      <c r="A150" s="43"/>
+      <c r="B150" s="49"/>
+      <c r="C150" s="46"/>
       <c r="D150" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E150" s="26"/>
     </row>
     <row r="151" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A151" s="47"/>
-      <c r="B151" s="40"/>
-      <c r="C151" s="42" t="s">
+      <c r="A151" s="43"/>
+      <c r="B151" s="49"/>
+      <c r="C151" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D151" s="28" t="s">
@@ -3983,31 +4005,31 @@
       <c r="E151" s="26"/>
     </row>
     <row r="152" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A152" s="47"/>
-      <c r="B152" s="40"/>
-      <c r="C152" s="43"/>
+      <c r="A152" s="43"/>
+      <c r="B152" s="49"/>
+      <c r="C152" s="46"/>
       <c r="D152" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E152" s="26"/>
     </row>
     <row r="153" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A153" s="47"/>
-      <c r="B153" s="40"/>
-      <c r="C153" s="43"/>
+      <c r="A153" s="43"/>
+      <c r="B153" s="49"/>
+      <c r="C153" s="46"/>
       <c r="D153" s="28" t="s">
         <v>104</v>
       </c>
       <c r="E153" s="26"/>
     </row>
     <row r="154" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A154" s="50" t="s">
+      <c r="A154" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="B154" s="41" t="s">
+      <c r="B154" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="C154" s="42" t="s">
+      <c r="C154" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D154" s="28" t="s">
@@ -4016,72 +4038,72 @@
       <c r="E154" s="26"/>
     </row>
     <row r="155" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A155" s="47"/>
-      <c r="B155" s="40"/>
-      <c r="C155" s="43"/>
+      <c r="A155" s="43"/>
+      <c r="B155" s="49"/>
+      <c r="C155" s="46"/>
       <c r="D155" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E155" s="26"/>
     </row>
     <row r="156" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A156" s="47"/>
-      <c r="B156" s="40"/>
-      <c r="C156" s="43"/>
+      <c r="A156" s="43"/>
+      <c r="B156" s="49"/>
+      <c r="C156" s="46"/>
       <c r="D156" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E156" s="26"/>
     </row>
     <row r="157" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A157" s="47"/>
-      <c r="B157" s="40"/>
-      <c r="C157" s="43"/>
+      <c r="A157" s="43"/>
+      <c r="B157" s="49"/>
+      <c r="C157" s="46"/>
       <c r="D157" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E157" s="26"/>
     </row>
     <row r="158" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A158" s="47"/>
-      <c r="B158" s="40"/>
-      <c r="C158" s="43"/>
+      <c r="A158" s="43"/>
+      <c r="B158" s="49"/>
+      <c r="C158" s="46"/>
       <c r="D158" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E158" s="26"/>
     </row>
     <row r="159" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A159" s="47"/>
-      <c r="B159" s="40"/>
-      <c r="C159" s="43"/>
+      <c r="A159" s="43"/>
+      <c r="B159" s="49"/>
+      <c r="C159" s="46"/>
       <c r="D159" s="28" t="s">
         <v>102</v>
       </c>
       <c r="E159" s="26"/>
     </row>
     <row r="160" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A160" s="47"/>
-      <c r="B160" s="40"/>
-      <c r="C160" s="43"/>
+      <c r="A160" s="43"/>
+      <c r="B160" s="49"/>
+      <c r="C160" s="46"/>
       <c r="D160" s="28" t="s">
         <v>168</v>
       </c>
       <c r="E160" s="26"/>
     </row>
     <row r="161" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A161" s="47"/>
-      <c r="B161" s="40"/>
-      <c r="C161" s="43"/>
+      <c r="A161" s="43"/>
+      <c r="B161" s="49"/>
+      <c r="C161" s="46"/>
       <c r="D161" s="28" t="s">
         <v>123</v>
       </c>
       <c r="E161" s="26"/>
     </row>
     <row r="162" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A162" s="47"/>
-      <c r="B162" s="40"/>
-      <c r="C162" s="51" t="s">
+      <c r="A162" s="43"/>
+      <c r="B162" s="49"/>
+      <c r="C162" s="47" t="s">
         <v>103</v>
       </c>
       <c r="D162" s="28" t="s">
@@ -4090,22 +4112,22 @@
       <c r="E162" s="26"/>
     </row>
     <row r="163" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A163" s="47"/>
-      <c r="B163" s="40"/>
-      <c r="C163" s="49"/>
+      <c r="A163" s="43"/>
+      <c r="B163" s="49"/>
+      <c r="C163" s="48"/>
       <c r="D163" s="28" t="s">
         <v>126</v>
       </c>
       <c r="E163" s="26"/>
     </row>
     <row r="164" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A164" s="50" t="s">
+      <c r="A164" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="B164" s="41" t="s">
+      <c r="B164" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="C164" s="42" t="s">
+      <c r="C164" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D164" s="28" t="s">
@@ -4114,40 +4136,40 @@
       <c r="E164" s="26"/>
     </row>
     <row r="165" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A165" s="47"/>
-      <c r="B165" s="40"/>
-      <c r="C165" s="43"/>
+      <c r="A165" s="43"/>
+      <c r="B165" s="49"/>
+      <c r="C165" s="46"/>
       <c r="D165" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E165" s="26"/>
     </row>
     <row r="166" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A166" s="47"/>
-      <c r="B166" s="40"/>
-      <c r="C166" s="43"/>
+      <c r="A166" s="43"/>
+      <c r="B166" s="49"/>
+      <c r="C166" s="46"/>
       <c r="D166" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E166" s="26"/>
     </row>
     <row r="167" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A167" s="47"/>
-      <c r="B167" s="40"/>
-      <c r="C167" s="43"/>
+      <c r="A167" s="43"/>
+      <c r="B167" s="49"/>
+      <c r="C167" s="46"/>
       <c r="D167" s="28" t="s">
         <v>96</v>
       </c>
       <c r="E167" s="26"/>
     </row>
     <row r="168" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A168" s="50" t="s">
+      <c r="A168" s="42" t="s">
         <v>129</v>
       </c>
-      <c r="B168" s="41" t="s">
+      <c r="B168" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C168" s="42" t="s">
+      <c r="C168" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D168" s="28" t="s">
@@ -4156,67 +4178,67 @@
       <c r="E168" s="26"/>
     </row>
     <row r="169" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A169" s="47"/>
-      <c r="B169" s="40"/>
-      <c r="C169" s="43"/>
+      <c r="A169" s="43"/>
+      <c r="B169" s="49"/>
+      <c r="C169" s="46"/>
       <c r="D169" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E169" s="26"/>
     </row>
     <row r="170" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A170" s="47"/>
-      <c r="B170" s="40"/>
-      <c r="C170" s="43"/>
+      <c r="A170" s="43"/>
+      <c r="B170" s="49"/>
+      <c r="C170" s="46"/>
       <c r="D170" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E170" s="26"/>
     </row>
     <row r="171" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A171" s="47"/>
-      <c r="B171" s="40"/>
-      <c r="C171" s="43"/>
+      <c r="A171" s="43"/>
+      <c r="B171" s="49"/>
+      <c r="C171" s="46"/>
       <c r="D171" s="28" t="s">
         <v>96</v>
       </c>
       <c r="E171" s="26"/>
     </row>
     <row r="172" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A172" s="47"/>
-      <c r="B172" s="40"/>
-      <c r="C172" s="43"/>
+      <c r="A172" s="43"/>
+      <c r="B172" s="49"/>
+      <c r="C172" s="46"/>
       <c r="D172" s="28" t="s">
         <v>130</v>
       </c>
       <c r="E172" s="26"/>
     </row>
     <row r="173" spans="1:5" ht="15.5" customHeight="1">
-      <c r="A173" s="47"/>
-      <c r="B173" s="40"/>
-      <c r="C173" s="43"/>
+      <c r="A173" s="43"/>
+      <c r="B173" s="49"/>
+      <c r="C173" s="46"/>
       <c r="D173" s="28" t="s">
         <v>82</v>
       </c>
       <c r="E173" s="26"/>
     </row>
     <row r="174" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A174" s="47"/>
-      <c r="B174" s="40"/>
-      <c r="C174" s="43"/>
+      <c r="A174" s="43"/>
+      <c r="B174" s="49"/>
+      <c r="C174" s="46"/>
       <c r="D174" s="28" t="s">
         <v>107</v>
       </c>
       <c r="E174" s="26"/>
     </row>
     <row r="175" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A175" s="50" t="s">
+      <c r="A175" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="B175" s="41" t="s">
+      <c r="B175" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="C175" s="42" t="s">
+      <c r="C175" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D175" s="28" t="s">
@@ -4225,81 +4247,81 @@
       <c r="E175" s="26"/>
     </row>
     <row r="176" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A176" s="47"/>
-      <c r="B176" s="40"/>
-      <c r="C176" s="43"/>
+      <c r="A176" s="43"/>
+      <c r="B176" s="49"/>
+      <c r="C176" s="46"/>
       <c r="D176" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E176" s="26"/>
     </row>
     <row r="177" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A177" s="47"/>
-      <c r="B177" s="40"/>
-      <c r="C177" s="43"/>
+      <c r="A177" s="43"/>
+      <c r="B177" s="49"/>
+      <c r="C177" s="46"/>
       <c r="D177" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E177" s="26"/>
     </row>
     <row r="178" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A178" s="47"/>
-      <c r="B178" s="40"/>
-      <c r="C178" s="43"/>
+      <c r="A178" s="43"/>
+      <c r="B178" s="49"/>
+      <c r="C178" s="46"/>
       <c r="D178" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E178" s="26"/>
     </row>
     <row r="179" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A179" s="47"/>
-      <c r="B179" s="40"/>
-      <c r="C179" s="43"/>
+      <c r="A179" s="43"/>
+      <c r="B179" s="49"/>
+      <c r="C179" s="46"/>
       <c r="D179" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E179" s="26"/>
     </row>
     <row r="180" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A180" s="47"/>
-      <c r="B180" s="40"/>
-      <c r="C180" s="43"/>
+      <c r="A180" s="43"/>
+      <c r="B180" s="49"/>
+      <c r="C180" s="46"/>
       <c r="D180" s="28" t="s">
         <v>102</v>
       </c>
       <c r="E180" s="26"/>
     </row>
     <row r="181" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A181" s="47"/>
-      <c r="B181" s="40"/>
-      <c r="C181" s="43"/>
+      <c r="A181" s="43"/>
+      <c r="B181" s="49"/>
+      <c r="C181" s="46"/>
       <c r="D181" s="28" t="s">
         <v>123</v>
       </c>
       <c r="E181" s="26"/>
     </row>
     <row r="182" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A182" s="47"/>
-      <c r="B182" s="40"/>
-      <c r="C182" s="43"/>
+      <c r="A182" s="43"/>
+      <c r="B182" s="49"/>
+      <c r="C182" s="46"/>
       <c r="D182" s="28" t="s">
         <v>169</v>
       </c>
       <c r="E182" s="26"/>
     </row>
     <row r="183" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A183" s="47"/>
-      <c r="B183" s="40"/>
-      <c r="C183" s="43"/>
+      <c r="A183" s="43"/>
+      <c r="B183" s="49"/>
+      <c r="C183" s="46"/>
       <c r="D183" s="32" t="s">
         <v>124</v>
       </c>
       <c r="E183" s="26"/>
     </row>
     <row r="184" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A184" s="47"/>
-      <c r="B184" s="40"/>
-      <c r="C184" s="51" t="s">
+      <c r="A184" s="43"/>
+      <c r="B184" s="49"/>
+      <c r="C184" s="47" t="s">
         <v>103</v>
       </c>
       <c r="D184" s="28" t="s">
@@ -4308,9 +4330,9 @@
       <c r="E184" s="26"/>
     </row>
     <row r="185" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A185" s="47"/>
-      <c r="B185" s="40"/>
-      <c r="C185" s="49"/>
+      <c r="A185" s="43"/>
+      <c r="B185" s="49"/>
+      <c r="C185" s="48"/>
       <c r="D185" s="28" t="s">
         <v>126</v>
       </c>
@@ -4328,13 +4350,13 @@
       <c r="E186" s="26"/>
     </row>
     <row r="187" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A187" s="50" t="s">
+      <c r="A187" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="B187" s="50" t="s">
+      <c r="B187" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="C187" s="42" t="s">
+      <c r="C187" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D187" s="28" t="s">
@@ -4343,72 +4365,72 @@
       <c r="E187" s="26"/>
     </row>
     <row r="188" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A188" s="47"/>
-      <c r="B188" s="47"/>
-      <c r="C188" s="43"/>
+      <c r="A188" s="43"/>
+      <c r="B188" s="43"/>
+      <c r="C188" s="46"/>
       <c r="D188" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E188" s="26"/>
     </row>
     <row r="189" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A189" s="47"/>
-      <c r="B189" s="47"/>
-      <c r="C189" s="43"/>
+      <c r="A189" s="43"/>
+      <c r="B189" s="43"/>
+      <c r="C189" s="46"/>
       <c r="D189" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E189" s="26"/>
     </row>
     <row r="190" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A190" s="47"/>
-      <c r="B190" s="47"/>
-      <c r="C190" s="43"/>
+      <c r="A190" s="43"/>
+      <c r="B190" s="43"/>
+      <c r="C190" s="46"/>
       <c r="D190" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E190" s="26"/>
     </row>
     <row r="191" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A191" s="47"/>
-      <c r="B191" s="47"/>
-      <c r="C191" s="43"/>
+      <c r="A191" s="43"/>
+      <c r="B191" s="43"/>
+      <c r="C191" s="46"/>
       <c r="D191" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E191" s="26"/>
     </row>
     <row r="192" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A192" s="47"/>
-      <c r="B192" s="47"/>
-      <c r="C192" s="43"/>
+      <c r="A192" s="43"/>
+      <c r="B192" s="43"/>
+      <c r="C192" s="46"/>
       <c r="D192" s="28" t="s">
         <v>102</v>
       </c>
       <c r="E192" s="26"/>
     </row>
     <row r="193" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A193" s="47"/>
-      <c r="B193" s="47"/>
-      <c r="C193" s="43"/>
+      <c r="A193" s="43"/>
+      <c r="B193" s="43"/>
+      <c r="C193" s="46"/>
       <c r="D193" s="28" t="s">
         <v>123</v>
       </c>
       <c r="E193" s="26"/>
     </row>
     <row r="194" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A194" s="47"/>
-      <c r="B194" s="47"/>
-      <c r="C194" s="43"/>
+      <c r="A194" s="43"/>
+      <c r="B194" s="43"/>
+      <c r="C194" s="46"/>
       <c r="D194" s="32" t="s">
         <v>172</v>
       </c>
       <c r="E194" s="26"/>
     </row>
     <row r="195" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A195" s="47"/>
-      <c r="B195" s="47"/>
-      <c r="C195" s="51" t="s">
+      <c r="A195" s="43"/>
+      <c r="B195" s="43"/>
+      <c r="C195" s="47" t="s">
         <v>103</v>
       </c>
       <c r="D195" s="28" t="s">
@@ -4417,28 +4439,28 @@
       <c r="E195" s="26"/>
     </row>
     <row r="196" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A196" s="47"/>
-      <c r="B196" s="47"/>
-      <c r="C196" s="49"/>
+      <c r="A196" s="43"/>
+      <c r="B196" s="43"/>
+      <c r="C196" s="48"/>
       <c r="D196" s="28" t="s">
         <v>126</v>
       </c>
       <c r="E196" s="26"/>
     </row>
     <row r="197" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A197" s="47"/>
-      <c r="B197" s="47"/>
+      <c r="A197" s="43"/>
+      <c r="B197" s="43"/>
       <c r="C197" s="33"/>
       <c r="D197" s="33"/>
       <c r="E197" s="26"/>
     </row>
     <row r="198" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A198" s="54" t="s">
+      <c r="A198" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="B198" s="55"/>
-      <c r="C198" s="55"/>
-      <c r="D198" s="55"/>
+      <c r="B198" s="41"/>
+      <c r="C198" s="41"/>
+      <c r="D198" s="41"/>
       <c r="E198" s="26"/>
     </row>
     <row r="199" spans="1:5" ht="14.5" customHeight="1">
@@ -4457,13 +4479,13 @@
       <c r="E199" s="26"/>
     </row>
     <row r="200" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A200" s="50" t="s">
+      <c r="A200" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="B200" s="41" t="s">
+      <c r="B200" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="C200" s="42" t="s">
+      <c r="C200" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D200" s="28" t="s">
@@ -4472,72 +4494,72 @@
       <c r="E200" s="26"/>
     </row>
     <row r="201" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A201" s="47"/>
-      <c r="B201" s="47"/>
-      <c r="C201" s="43"/>
+      <c r="A201" s="43"/>
+      <c r="B201" s="43"/>
+      <c r="C201" s="46"/>
       <c r="D201" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E201" s="26"/>
     </row>
     <row r="202" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A202" s="47"/>
-      <c r="B202" s="47"/>
-      <c r="C202" s="43"/>
+      <c r="A202" s="43"/>
+      <c r="B202" s="43"/>
+      <c r="C202" s="46"/>
       <c r="D202" s="28" t="s">
         <v>99</v>
       </c>
       <c r="E202" s="26"/>
     </row>
     <row r="203" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A203" s="47"/>
-      <c r="B203" s="47"/>
-      <c r="C203" s="43"/>
+      <c r="A203" s="43"/>
+      <c r="B203" s="43"/>
+      <c r="C203" s="46"/>
       <c r="D203" s="28" t="s">
         <v>100</v>
       </c>
       <c r="E203" s="26"/>
     </row>
     <row r="204" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A204" s="47"/>
-      <c r="B204" s="47"/>
-      <c r="C204" s="43"/>
+      <c r="A204" s="43"/>
+      <c r="B204" s="43"/>
+      <c r="C204" s="46"/>
       <c r="D204" s="28" t="s">
         <v>101</v>
       </c>
       <c r="E204" s="26"/>
     </row>
     <row r="205" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A205" s="47"/>
-      <c r="B205" s="47"/>
-      <c r="C205" s="43"/>
+      <c r="A205" s="43"/>
+      <c r="B205" s="43"/>
+      <c r="C205" s="46"/>
       <c r="D205" s="28" t="s">
         <v>102</v>
       </c>
       <c r="E205" s="26"/>
     </row>
     <row r="206" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A206" s="47"/>
-      <c r="B206" s="47"/>
-      <c r="C206" s="43"/>
+      <c r="A206" s="43"/>
+      <c r="B206" s="43"/>
+      <c r="C206" s="46"/>
       <c r="D206" s="28" t="s">
         <v>123</v>
       </c>
       <c r="E206" s="26"/>
     </row>
     <row r="207" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A207" s="47"/>
-      <c r="B207" s="47"/>
-      <c r="C207" s="43"/>
+      <c r="A207" s="43"/>
+      <c r="B207" s="43"/>
+      <c r="C207" s="46"/>
       <c r="D207" s="32" t="s">
         <v>124</v>
       </c>
       <c r="E207" s="26"/>
     </row>
     <row r="208" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A208" s="47"/>
-      <c r="B208" s="47"/>
-      <c r="C208" s="51" t="s">
+      <c r="A208" s="43"/>
+      <c r="B208" s="43"/>
+      <c r="C208" s="47" t="s">
         <v>103</v>
       </c>
       <c r="D208" s="28" t="s">
@@ -4546,21 +4568,21 @@
       <c r="E208" s="26"/>
     </row>
     <row r="209" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A209" s="47"/>
-      <c r="B209" s="47"/>
-      <c r="C209" s="49"/>
+      <c r="A209" s="43"/>
+      <c r="B209" s="43"/>
+      <c r="C209" s="48"/>
       <c r="D209" s="28" t="s">
         <v>126</v>
       </c>
       <c r="E209" s="26"/>
     </row>
     <row r="210" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A210" s="52" t="s">
+      <c r="A210" s="38" t="s">
         <v>173</v>
       </c>
-      <c r="B210" s="53"/>
-      <c r="C210" s="53"/>
-      <c r="D210" s="53"/>
+      <c r="B210" s="39"/>
+      <c r="C210" s="39"/>
+      <c r="D210" s="39"/>
       <c r="E210" s="26"/>
     </row>
     <row r="211" spans="1:5" ht="14.5" customHeight="1">
@@ -4601,12 +4623,12 @@
       <c r="E213" s="26"/>
     </row>
     <row r="214" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A214" s="54" t="s">
+      <c r="A214" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="B214" s="55"/>
-      <c r="C214" s="55"/>
-      <c r="D214" s="55"/>
+      <c r="B214" s="41"/>
+      <c r="C214" s="41"/>
+      <c r="D214" s="41"/>
       <c r="E214" s="26"/>
     </row>
     <row r="215" spans="1:5" ht="14.5" customHeight="1">
@@ -4670,21 +4692,57 @@
     </row>
   </sheetData>
   <mergeCells count="77">
-    <mergeCell ref="A210:D210"/>
-    <mergeCell ref="A214:D214"/>
-    <mergeCell ref="A198:D198"/>
-    <mergeCell ref="A200:A209"/>
-    <mergeCell ref="B200:B209"/>
-    <mergeCell ref="C200:C207"/>
-    <mergeCell ref="C208:C209"/>
-    <mergeCell ref="A175:A185"/>
-    <mergeCell ref="B175:B185"/>
-    <mergeCell ref="C175:C183"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="A187:A197"/>
-    <mergeCell ref="B187:B197"/>
-    <mergeCell ref="C187:C194"/>
-    <mergeCell ref="C195:C196"/>
+    <mergeCell ref="A168:A174"/>
+    <mergeCell ref="B168:B174"/>
+    <mergeCell ref="C168:C174"/>
+    <mergeCell ref="A154:A163"/>
+    <mergeCell ref="B154:B163"/>
+    <mergeCell ref="C154:C161"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="A164:A167"/>
+    <mergeCell ref="B164:B167"/>
+    <mergeCell ref="C164:C167"/>
+    <mergeCell ref="A112:A124"/>
+    <mergeCell ref="B112:B124"/>
+    <mergeCell ref="C112:C118"/>
+    <mergeCell ref="C119:C121"/>
+    <mergeCell ref="C122:C124"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="B3:B15"/>
+    <mergeCell ref="A3:A15"/>
+    <mergeCell ref="C16:C22"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="A16:A28"/>
+    <mergeCell ref="B16:B28"/>
+    <mergeCell ref="A63:A85"/>
+    <mergeCell ref="B63:B85"/>
+    <mergeCell ref="C63:C69"/>
+    <mergeCell ref="C70:C77"/>
+    <mergeCell ref="C78:C85"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="A46:A62"/>
+    <mergeCell ref="B46:B62"/>
+    <mergeCell ref="C53:C57"/>
+    <mergeCell ref="C58:C62"/>
+    <mergeCell ref="A29:A45"/>
+    <mergeCell ref="B29:B45"/>
+    <mergeCell ref="C46:C52"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="B86:B98"/>
+    <mergeCell ref="C86:C92"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="A99:A111"/>
+    <mergeCell ref="B99:B111"/>
+    <mergeCell ref="C99:C105"/>
+    <mergeCell ref="C106:C108"/>
+    <mergeCell ref="C109:C111"/>
+    <mergeCell ref="A86:A98"/>
     <mergeCell ref="C125:C131"/>
     <mergeCell ref="C132:C134"/>
     <mergeCell ref="C135:C137"/>
@@ -4696,57 +4754,21 @@
     <mergeCell ref="C151:C153"/>
     <mergeCell ref="A125:A137"/>
     <mergeCell ref="B125:B137"/>
-    <mergeCell ref="B86:B98"/>
-    <mergeCell ref="C86:C92"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="C96:C98"/>
-    <mergeCell ref="A99:A111"/>
-    <mergeCell ref="B99:B111"/>
-    <mergeCell ref="C99:C105"/>
-    <mergeCell ref="C106:C108"/>
-    <mergeCell ref="C109:C111"/>
-    <mergeCell ref="A86:A98"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="A46:A62"/>
-    <mergeCell ref="B46:B62"/>
-    <mergeCell ref="C53:C57"/>
-    <mergeCell ref="C58:C62"/>
-    <mergeCell ref="A29:A45"/>
-    <mergeCell ref="B29:B45"/>
-    <mergeCell ref="C46:C52"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="A63:A85"/>
-    <mergeCell ref="B63:B85"/>
-    <mergeCell ref="C63:C69"/>
-    <mergeCell ref="C70:C77"/>
-    <mergeCell ref="C78:C85"/>
-    <mergeCell ref="C16:C22"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="A16:A28"/>
-    <mergeCell ref="B16:B28"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="B3:B15"/>
-    <mergeCell ref="A3:A15"/>
-    <mergeCell ref="A112:A124"/>
-    <mergeCell ref="B112:B124"/>
-    <mergeCell ref="C112:C118"/>
-    <mergeCell ref="C119:C121"/>
-    <mergeCell ref="C122:C124"/>
-    <mergeCell ref="A168:A174"/>
-    <mergeCell ref="B168:B174"/>
-    <mergeCell ref="C168:C174"/>
-    <mergeCell ref="A154:A163"/>
-    <mergeCell ref="B154:B163"/>
-    <mergeCell ref="C154:C161"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="A164:A167"/>
-    <mergeCell ref="B164:B167"/>
-    <mergeCell ref="C164:C167"/>
+    <mergeCell ref="A175:A185"/>
+    <mergeCell ref="B175:B185"/>
+    <mergeCell ref="C175:C183"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="A187:A197"/>
+    <mergeCell ref="B187:B197"/>
+    <mergeCell ref="C187:C194"/>
+    <mergeCell ref="C195:C196"/>
+    <mergeCell ref="A210:D210"/>
+    <mergeCell ref="A214:D214"/>
+    <mergeCell ref="A198:D198"/>
+    <mergeCell ref="A200:A209"/>
+    <mergeCell ref="B200:B209"/>
+    <mergeCell ref="C200:C207"/>
+    <mergeCell ref="C208:C209"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -4766,16 +4788,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -4788,13 +4810,13 @@
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -4852,11 +4874,11 @@
       <c r="R4" s="2"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="2"/>
@@ -4874,13 +4896,13 @@
       <c r="R5" s="2"/>
     </row>
     <row r="6" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -4898,16 +4920,16 @@
       <c r="R6" s="2"/>
     </row>
     <row r="7" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A7" s="60" t="s">
+      <c r="A7" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
       <c r="I7" s="5" t="s">
         <v>7</v>
       </c>
@@ -4922,15 +4944,15 @@
       <c r="R7" s="2"/>
     </row>
     <row r="8" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -4944,14 +4966,14 @@
       <c r="R8" s="2"/>
     </row>
     <row r="9" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A9" s="56" t="s">
+      <c r="A9" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -4966,15 +4988,15 @@
       <c r="R9" s="2"/>
     </row>
     <row r="10" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -5012,12 +5034,12 @@
       <c r="R11" s="2"/>
     </row>
     <row r="12" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A12" s="56" t="s">
+      <c r="A12" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -5034,16 +5056,16 @@
       <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -5056,16 +5078,16 @@
       <c r="R13" s="2"/>
     </row>
     <row r="14" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -5078,16 +5100,16 @@
       <c r="R14" s="2"/>
     </row>
     <row r="15" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A15" s="56" t="s">
+      <c r="A15" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -5100,16 +5122,16 @@
       <c r="R15" s="2"/>
     </row>
     <row r="16" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -5122,60 +5144,60 @@
       <c r="R16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
-      <c r="L17" s="57"/>
-      <c r="M17" s="57"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="57"/>
-      <c r="P17" s="57"/>
-      <c r="Q17" s="57"/>
-      <c r="R17" s="57"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="58"/>
+      <c r="R17" s="58"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="57"/>
-      <c r="M18" s="57"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="57"/>
-      <c r="P18" s="57"/>
-      <c r="Q18" s="57"/>
-      <c r="R18" s="57"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="58"/>
+      <c r="L18" s="58"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="58"/>
+      <c r="O18" s="58"/>
+      <c r="P18" s="58"/>
+      <c r="Q18" s="58"/>
+      <c r="R18" s="58"/>
     </row>
     <row r="19" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A19" s="61" t="s">
+      <c r="A19" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -5188,38 +5210,38 @@
       <c r="R19" s="2"/>
     </row>
     <row r="20" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="57"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="57"/>
-      <c r="N20" s="57"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="58"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
     </row>
     <row r="21" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A21" s="56" t="s">
+      <c r="A21" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -5232,14 +5254,14 @@
       <c r="R21" s="2"/>
     </row>
     <row r="22" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A22" s="61" t="s">
+      <c r="A22" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="57"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -5298,14 +5320,14 @@
       <c r="R24" s="2"/>
     </row>
     <row r="25" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A25" s="63" t="s">
+      <c r="A25" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -5386,16 +5408,16 @@
       <c r="R28" s="2"/>
     </row>
     <row r="29" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A29" s="56" t="s">
+      <c r="A29" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -5430,20 +5452,20 @@
       <c r="R30" s="2"/>
     </row>
     <row r="31" spans="1:18" ht="13.5" customHeight="1">
-      <c r="A31" s="56" t="s">
+      <c r="A31" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="57"/>
-      <c r="C31" s="57"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="57"/>
-      <c r="L31" s="57"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5453,6 +5475,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="A31:L31"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A6:E6"/>
@@ -5469,12 +5497,6 @@
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -6523,15 +6545,15 @@
       <c r="A28" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="64" t="s">
+      <c r="B28" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="65"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="65"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
       <c r="I28" s="22"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -6990,14 +7012,14 @@
       <c r="X1" s="2"/>
     </row>
     <row r="2" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -7046,19 +7068,19 @@
       <c r="X3" s="2"/>
     </row>
     <row r="4" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -7074,43 +7096,43 @@
       <c r="X4" s="2"/>
     </row>
     <row r="5" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="67" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
-      <c r="P5" s="57"/>
-      <c r="Q5" s="57"/>
-      <c r="R5" s="57"/>
-      <c r="S5" s="57"/>
-      <c r="T5" s="57"/>
-      <c r="U5" s="57"/>
-      <c r="V5" s="57"/>
-      <c r="W5" s="57"/>
-      <c r="X5" s="57"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="58"/>
+      <c r="Q5" s="58"/>
+      <c r="R5" s="58"/>
+      <c r="S5" s="58"/>
+      <c r="T5" s="58"/>
+      <c r="U5" s="58"/>
+      <c r="V5" s="58"/>
+      <c r="W5" s="58"/>
+      <c r="X5" s="58"/>
     </row>
     <row r="6" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -7130,21 +7152,21 @@
       <c r="X6" s="2"/>
     </row>
     <row r="7" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="67" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="57"/>
-      <c r="L7" s="57"/>
-      <c r="M7" s="57"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="58"/>
+      <c r="M7" s="58"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -7158,15 +7180,15 @@
       <c r="X7" s="2"/>
     </row>
     <row r="8" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -7186,14 +7208,14 @@
       <c r="X8" s="2"/>
     </row>
     <row r="9" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="71" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -7214,14 +7236,14 @@
       <c r="X9" s="2"/>
     </row>
     <row r="10" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="67" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -7242,13 +7264,13 @@
       <c r="X10" s="2"/>
     </row>
     <row r="11" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -7270,15 +7292,15 @@
       <c r="X11" s="2"/>
     </row>
     <row r="12" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -7298,14 +7320,14 @@
       <c r="X12" s="2"/>
     </row>
     <row r="13" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -7326,15 +7348,15 @@
       <c r="X13" s="2"/>
     </row>
     <row r="14" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A14" s="68" t="s">
+      <c r="A14" s="71" t="s">
         <v>153</v>
       </c>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -7354,16 +7376,16 @@
       <c r="X14" s="2"/>
     </row>
     <row r="15" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="71" t="s">
         <v>154</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -7382,16 +7404,16 @@
       <c r="X15" s="2"/>
     </row>
     <row r="16" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -7410,13 +7432,13 @@
       <c r="X16" s="2"/>
     </row>
     <row r="17" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -7438,14 +7460,14 @@
       <c r="X17" s="2"/>
     </row>
     <row r="18" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A18" s="66" t="s">
+      <c r="A18" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="B18" s="67"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="67"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -7466,13 +7488,13 @@
       <c r="X18" s="2"/>
     </row>
     <row r="19" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A19" s="68" t="s">
+      <c r="A19" s="71" t="s">
         <v>158</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -7494,18 +7516,18 @@
       <c r="X19" s="2"/>
     </row>
     <row r="20" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A20" s="66" t="s">
+      <c r="A20" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="B20" s="67"/>
-      <c r="C20" s="67"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="67"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -7522,21 +7544,21 @@
       <c r="X20" s="2"/>
     </row>
     <row r="21" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A21" s="66" t="s">
+      <c r="A21" s="67" t="s">
         <v>160</v>
       </c>
-      <c r="B21" s="67"/>
-      <c r="C21" s="67"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="67"/>
-      <c r="K21" s="67"/>
-      <c r="L21" s="67"/>
-      <c r="M21" s="67"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="68"/>
+      <c r="M21" s="68"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -7634,14 +7656,14 @@
       <c r="X24" s="2"/>
     </row>
     <row r="25" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A25" s="66" t="s">
+      <c r="A25" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -7691,6 +7713,16 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:F2"/>
@@ -7703,16 +7735,6 @@
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A21:M21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -7733,13 +7755,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="103"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" ht="15.5">
       <c r="A2" s="27" t="s">
@@ -7754,75 +7776,75 @@
       <c r="D2" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="103"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="3" spans="1:5" ht="15.5">
-      <c r="A3" s="74">
+      <c r="A3" s="93">
         <v>1</v>
       </c>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="80" t="s">
+      <c r="C3" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D3" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="103"/>
+      <c r="E3" s="78"/>
     </row>
     <row r="4" spans="1:5" ht="15.5">
-      <c r="A4" s="75"/>
-      <c r="B4" s="78"/>
-      <c r="C4" s="81"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="83"/>
       <c r="D4" s="28" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.5">
-      <c r="A5" s="75"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="81"/>
+      <c r="A5" s="94"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="83"/>
       <c r="D5" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.5">
-      <c r="A6" s="75"/>
-      <c r="B6" s="78"/>
-      <c r="C6" s="81"/>
+      <c r="A6" s="94"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="83"/>
       <c r="D6" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.5">
-      <c r="A7" s="75"/>
-      <c r="B7" s="78"/>
-      <c r="C7" s="81"/>
+      <c r="A7" s="94"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="83"/>
       <c r="D7" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.5">
-      <c r="A8" s="75"/>
-      <c r="B8" s="78"/>
-      <c r="C8" s="81"/>
+      <c r="A8" s="94"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="83"/>
       <c r="D8" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.5">
-      <c r="A9" s="75"/>
-      <c r="B9" s="78"/>
-      <c r="C9" s="82"/>
+      <c r="A9" s="94"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="84"/>
       <c r="D9" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.5">
-      <c r="A10" s="75"/>
-      <c r="B10" s="78"/>
-      <c r="C10" s="80" t="s">
+      <c r="A10" s="94"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="82" t="s">
         <v>103</v>
       </c>
       <c r="D10" s="28" t="s">
@@ -7830,25 +7852,25 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.5">
-      <c r="A11" s="75"/>
-      <c r="B11" s="78"/>
-      <c r="C11" s="81"/>
+      <c r="A11" s="94"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="83"/>
       <c r="D11" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.5">
-      <c r="A12" s="75"/>
-      <c r="B12" s="78"/>
-      <c r="C12" s="82"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="84"/>
       <c r="D12" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.5">
-      <c r="A13" s="75"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="80" t="s">
+      <c r="A13" s="94"/>
+      <c r="B13" s="88"/>
+      <c r="C13" s="82" t="s">
         <v>96</v>
       </c>
       <c r="D13" s="28" t="s">
@@ -7856,29 +7878,29 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.5">
-      <c r="A14" s="75"/>
-      <c r="B14" s="78"/>
-      <c r="C14" s="81"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="83"/>
       <c r="D14" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.5">
-      <c r="A15" s="76"/>
-      <c r="B15" s="79"/>
-      <c r="C15" s="82"/>
+      <c r="A15" s="95"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="84"/>
       <c r="D15" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.5">
-      <c r="A16" s="74">
+      <c r="A16" s="93">
         <v>2</v>
       </c>
-      <c r="B16" s="77" t="s">
+      <c r="B16" s="87" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="80" t="s">
+      <c r="C16" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D16" s="28" t="s">
@@ -7886,57 +7908,57 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.5">
-      <c r="A17" s="75"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="81"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="88"/>
+      <c r="C17" s="83"/>
       <c r="D17" s="28" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.5">
-      <c r="A18" s="75"/>
-      <c r="B18" s="78"/>
-      <c r="C18" s="81"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="88"/>
+      <c r="C18" s="83"/>
       <c r="D18" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.5">
-      <c r="A19" s="75"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="81"/>
+      <c r="A19" s="94"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="83"/>
       <c r="D19" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.5">
-      <c r="A20" s="75"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="81"/>
+      <c r="A20" s="94"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="83"/>
       <c r="D20" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.5">
-      <c r="A21" s="75"/>
-      <c r="B21" s="78"/>
-      <c r="C21" s="81"/>
+      <c r="A21" s="94"/>
+      <c r="B21" s="88"/>
+      <c r="C21" s="83"/>
       <c r="D21" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.5">
-      <c r="A22" s="75"/>
-      <c r="B22" s="78"/>
-      <c r="C22" s="82"/>
+      <c r="A22" s="94"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="84"/>
       <c r="D22" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.5">
-      <c r="A23" s="75"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="80" t="s">
+      <c r="A23" s="94"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="82" t="s">
         <v>103</v>
       </c>
       <c r="D23" s="28" t="s">
@@ -7944,25 +7966,25 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.5">
-      <c r="A24" s="75"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="81"/>
+      <c r="A24" s="94"/>
+      <c r="B24" s="88"/>
+      <c r="C24" s="83"/>
       <c r="D24" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.5">
-      <c r="A25" s="75"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="82"/>
+      <c r="A25" s="94"/>
+      <c r="B25" s="88"/>
+      <c r="C25" s="84"/>
       <c r="D25" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.5">
-      <c r="A26" s="75"/>
-      <c r="B26" s="78"/>
-      <c r="C26" s="80" t="s">
+      <c r="A26" s="94"/>
+      <c r="B26" s="88"/>
+      <c r="C26" s="82" t="s">
         <v>96</v>
       </c>
       <c r="D26" s="28" t="s">
@@ -7970,29 +7992,29 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.5">
-      <c r="A27" s="75"/>
-      <c r="B27" s="78"/>
-      <c r="C27" s="81"/>
+      <c r="A27" s="94"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="83"/>
       <c r="D27" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.5">
-      <c r="A28" s="76"/>
-      <c r="B28" s="79"/>
-      <c r="C28" s="82"/>
+      <c r="A28" s="95"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="84"/>
       <c r="D28" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.5">
-      <c r="A29" s="83">
+      <c r="A29" s="96">
         <v>3</v>
       </c>
-      <c r="B29" s="86" t="s">
+      <c r="B29" s="99" t="s">
         <v>166</v>
       </c>
-      <c r="C29" s="80" t="s">
+      <c r="C29" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D29" s="28" t="s">
@@ -8000,57 +8022,57 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.5">
-      <c r="A30" s="84"/>
-      <c r="B30" s="87"/>
-      <c r="C30" s="81"/>
+      <c r="A30" s="97"/>
+      <c r="B30" s="100"/>
+      <c r="C30" s="83"/>
       <c r="D30" s="28" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.5">
-      <c r="A31" s="84"/>
-      <c r="B31" s="87"/>
-      <c r="C31" s="81"/>
+      <c r="A31" s="97"/>
+      <c r="B31" s="100"/>
+      <c r="C31" s="83"/>
       <c r="D31" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.5">
-      <c r="A32" s="84"/>
-      <c r="B32" s="87"/>
-      <c r="C32" s="81"/>
+      <c r="A32" s="97"/>
+      <c r="B32" s="100"/>
+      <c r="C32" s="83"/>
       <c r="D32" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.5">
-      <c r="A33" s="84"/>
-      <c r="B33" s="87"/>
-      <c r="C33" s="81"/>
+      <c r="A33" s="97"/>
+      <c r="B33" s="100"/>
+      <c r="C33" s="83"/>
       <c r="D33" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.5">
-      <c r="A34" s="84"/>
-      <c r="B34" s="87"/>
-      <c r="C34" s="81"/>
+      <c r="A34" s="97"/>
+      <c r="B34" s="100"/>
+      <c r="C34" s="83"/>
       <c r="D34" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.5">
-      <c r="A35" s="84"/>
-      <c r="B35" s="87"/>
-      <c r="C35" s="82"/>
+      <c r="A35" s="97"/>
+      <c r="B35" s="100"/>
+      <c r="C35" s="84"/>
       <c r="D35" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15.5">
-      <c r="A36" s="84"/>
-      <c r="B36" s="87"/>
-      <c r="C36" s="80" t="s">
+      <c r="A36" s="97"/>
+      <c r="B36" s="100"/>
+      <c r="C36" s="82" t="s">
         <v>103</v>
       </c>
       <c r="D36" s="28" t="s">
@@ -8058,25 +8080,25 @@
       </c>
     </row>
     <row r="37" spans="1:4" ht="15.5">
-      <c r="A37" s="84"/>
-      <c r="B37" s="87"/>
-      <c r="C37" s="81"/>
+      <c r="A37" s="97"/>
+      <c r="B37" s="100"/>
+      <c r="C37" s="83"/>
       <c r="D37" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.5">
-      <c r="A38" s="84"/>
-      <c r="B38" s="87"/>
-      <c r="C38" s="82"/>
+      <c r="A38" s="97"/>
+      <c r="B38" s="100"/>
+      <c r="C38" s="84"/>
       <c r="D38" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.5">
-      <c r="A39" s="84"/>
-      <c r="B39" s="87"/>
-      <c r="C39" s="80" t="s">
+      <c r="A39" s="97"/>
+      <c r="B39" s="100"/>
+      <c r="C39" s="82" t="s">
         <v>96</v>
       </c>
       <c r="D39" s="28" t="s">
@@ -8084,29 +8106,29 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.5">
-      <c r="A40" s="84"/>
-      <c r="B40" s="87"/>
-      <c r="C40" s="81"/>
+      <c r="A40" s="97"/>
+      <c r="B40" s="100"/>
+      <c r="C40" s="83"/>
       <c r="D40" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.5">
-      <c r="A41" s="85"/>
-      <c r="B41" s="88"/>
-      <c r="C41" s="82"/>
+      <c r="A41" s="98"/>
+      <c r="B41" s="101"/>
+      <c r="C41" s="84"/>
       <c r="D41" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.5">
-      <c r="A42" s="74">
+      <c r="A42" s="93">
         <v>4</v>
       </c>
-      <c r="B42" s="77" t="s">
+      <c r="B42" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="80" t="s">
+      <c r="C42" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D42" s="28" t="s">
@@ -8114,57 +8136,57 @@
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.5">
-      <c r="A43" s="75"/>
-      <c r="B43" s="78"/>
-      <c r="C43" s="81"/>
+      <c r="A43" s="94"/>
+      <c r="B43" s="88"/>
+      <c r="C43" s="83"/>
       <c r="D43" s="28" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.5">
-      <c r="A44" s="75"/>
-      <c r="B44" s="78"/>
-      <c r="C44" s="81"/>
+      <c r="A44" s="94"/>
+      <c r="B44" s="88"/>
+      <c r="C44" s="83"/>
       <c r="D44" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.5">
-      <c r="A45" s="75"/>
-      <c r="B45" s="78"/>
-      <c r="C45" s="81"/>
+      <c r="A45" s="94"/>
+      <c r="B45" s="88"/>
+      <c r="C45" s="83"/>
       <c r="D45" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15.5">
-      <c r="A46" s="75"/>
-      <c r="B46" s="78"/>
-      <c r="C46" s="81"/>
+      <c r="A46" s="94"/>
+      <c r="B46" s="88"/>
+      <c r="C46" s="83"/>
       <c r="D46" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.5">
-      <c r="A47" s="75"/>
-      <c r="B47" s="78"/>
-      <c r="C47" s="81"/>
+      <c r="A47" s="94"/>
+      <c r="B47" s="88"/>
+      <c r="C47" s="83"/>
       <c r="D47" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.5">
-      <c r="A48" s="75"/>
-      <c r="B48" s="78"/>
-      <c r="C48" s="82"/>
+      <c r="A48" s="94"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="84"/>
       <c r="D48" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.5">
-      <c r="A49" s="75"/>
-      <c r="B49" s="78"/>
-      <c r="C49" s="80" t="s">
+      <c r="A49" s="94"/>
+      <c r="B49" s="88"/>
+      <c r="C49" s="82" t="s">
         <v>103</v>
       </c>
       <c r="D49" s="28" t="s">
@@ -8172,41 +8194,41 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="15.5">
-      <c r="A50" s="75"/>
-      <c r="B50" s="78"/>
-      <c r="C50" s="81"/>
+      <c r="A50" s="94"/>
+      <c r="B50" s="88"/>
+      <c r="C50" s="83"/>
       <c r="D50" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15.5">
-      <c r="A51" s="75"/>
-      <c r="B51" s="78"/>
-      <c r="C51" s="81"/>
+      <c r="A51" s="94"/>
+      <c r="B51" s="88"/>
+      <c r="C51" s="83"/>
       <c r="D51" s="28" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.5">
-      <c r="A52" s="75"/>
-      <c r="B52" s="78"/>
-      <c r="C52" s="81"/>
+      <c r="A52" s="94"/>
+      <c r="B52" s="88"/>
+      <c r="C52" s="83"/>
       <c r="D52" s="28" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15.5">
-      <c r="A53" s="75"/>
-      <c r="B53" s="78"/>
-      <c r="C53" s="82"/>
+      <c r="A53" s="94"/>
+      <c r="B53" s="88"/>
+      <c r="C53" s="84"/>
       <c r="D53" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.5">
-      <c r="A54" s="75"/>
-      <c r="B54" s="78"/>
-      <c r="C54" s="80" t="s">
+      <c r="A54" s="94"/>
+      <c r="B54" s="88"/>
+      <c r="C54" s="82" t="s">
         <v>96</v>
       </c>
       <c r="D54" s="28" t="s">
@@ -8214,45 +8236,45 @@
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.5">
-      <c r="A55" s="75"/>
-      <c r="B55" s="78"/>
-      <c r="C55" s="81"/>
+      <c r="A55" s="94"/>
+      <c r="B55" s="88"/>
+      <c r="C55" s="83"/>
       <c r="D55" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.5">
-      <c r="A56" s="75"/>
-      <c r="B56" s="78"/>
-      <c r="C56" s="81"/>
+      <c r="A56" s="94"/>
+      <c r="B56" s="88"/>
+      <c r="C56" s="83"/>
       <c r="D56" s="28" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.5">
-      <c r="A57" s="75"/>
-      <c r="B57" s="78"/>
-      <c r="C57" s="81"/>
+      <c r="A57" s="94"/>
+      <c r="B57" s="88"/>
+      <c r="C57" s="83"/>
       <c r="D57" s="28" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15.5">
-      <c r="A58" s="76"/>
-      <c r="B58" s="79"/>
-      <c r="C58" s="82"/>
+      <c r="A58" s="95"/>
+      <c r="B58" s="89"/>
+      <c r="C58" s="84"/>
       <c r="D58" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.5">
-      <c r="A59" s="74">
+      <c r="A59" s="93">
         <v>5</v>
       </c>
-      <c r="B59" s="77" t="s">
+      <c r="B59" s="87" t="s">
         <v>108</v>
       </c>
-      <c r="C59" s="80" t="s">
+      <c r="C59" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D59" s="28" t="s">
@@ -8260,57 +8282,57 @@
       </c>
     </row>
     <row r="60" spans="1:4" ht="15.5">
-      <c r="A60" s="75"/>
-      <c r="B60" s="78"/>
-      <c r="C60" s="81"/>
+      <c r="A60" s="94"/>
+      <c r="B60" s="88"/>
+      <c r="C60" s="83"/>
       <c r="D60" s="28" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.5">
-      <c r="A61" s="75"/>
-      <c r="B61" s="78"/>
-      <c r="C61" s="81"/>
+      <c r="A61" s="94"/>
+      <c r="B61" s="88"/>
+      <c r="C61" s="83"/>
       <c r="D61" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.5">
-      <c r="A62" s="75"/>
-      <c r="B62" s="78"/>
-      <c r="C62" s="81"/>
+      <c r="A62" s="94"/>
+      <c r="B62" s="88"/>
+      <c r="C62" s="83"/>
       <c r="D62" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.5">
-      <c r="A63" s="75"/>
-      <c r="B63" s="78"/>
-      <c r="C63" s="81"/>
+      <c r="A63" s="94"/>
+      <c r="B63" s="88"/>
+      <c r="C63" s="83"/>
       <c r="D63" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.5">
-      <c r="A64" s="75"/>
-      <c r="B64" s="78"/>
-      <c r="C64" s="81"/>
+      <c r="A64" s="94"/>
+      <c r="B64" s="88"/>
+      <c r="C64" s="83"/>
       <c r="D64" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15.5">
-      <c r="A65" s="75"/>
-      <c r="B65" s="78"/>
-      <c r="C65" s="82"/>
+      <c r="A65" s="94"/>
+      <c r="B65" s="88"/>
+      <c r="C65" s="84"/>
       <c r="D65" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.5">
-      <c r="A66" s="75"/>
-      <c r="B66" s="78"/>
-      <c r="C66" s="80" t="s">
+      <c r="A66" s="94"/>
+      <c r="B66" s="88"/>
+      <c r="C66" s="82" t="s">
         <v>103</v>
       </c>
       <c r="D66" s="28" t="s">
@@ -8318,65 +8340,65 @@
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.5">
-      <c r="A67" s="75"/>
-      <c r="B67" s="78"/>
-      <c r="C67" s="81"/>
+      <c r="A67" s="94"/>
+      <c r="B67" s="88"/>
+      <c r="C67" s="83"/>
       <c r="D67" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.5">
-      <c r="A68" s="75"/>
-      <c r="B68" s="78"/>
-      <c r="C68" s="81"/>
+      <c r="A68" s="94"/>
+      <c r="B68" s="88"/>
+      <c r="C68" s="83"/>
       <c r="D68" s="28" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.5">
-      <c r="A69" s="75"/>
-      <c r="B69" s="78"/>
-      <c r="C69" s="81"/>
+      <c r="A69" s="94"/>
+      <c r="B69" s="88"/>
+      <c r="C69" s="83"/>
       <c r="D69" s="28" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.5">
-      <c r="A70" s="75"/>
-      <c r="B70" s="78"/>
-      <c r="C70" s="81"/>
+      <c r="A70" s="94"/>
+      <c r="B70" s="88"/>
+      <c r="C70" s="83"/>
       <c r="D70" s="28" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.5">
-      <c r="A71" s="75"/>
-      <c r="B71" s="78"/>
-      <c r="C71" s="81"/>
+      <c r="A71" s="94"/>
+      <c r="B71" s="88"/>
+      <c r="C71" s="83"/>
       <c r="D71" s="28" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.5">
-      <c r="A72" s="75"/>
-      <c r="B72" s="78"/>
-      <c r="C72" s="81"/>
+      <c r="A72" s="94"/>
+      <c r="B72" s="88"/>
+      <c r="C72" s="83"/>
       <c r="D72" s="28" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.5">
-      <c r="A73" s="75"/>
-      <c r="B73" s="78"/>
-      <c r="C73" s="82"/>
+      <c r="A73" s="94"/>
+      <c r="B73" s="88"/>
+      <c r="C73" s="84"/>
       <c r="D73" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15.5">
-      <c r="A74" s="75"/>
-      <c r="B74" s="78"/>
-      <c r="C74" s="80" t="s">
+      <c r="A74" s="94"/>
+      <c r="B74" s="88"/>
+      <c r="C74" s="82" t="s">
         <v>96</v>
       </c>
       <c r="D74" s="28" t="s">
@@ -8384,69 +8406,69 @@
       </c>
     </row>
     <row r="75" spans="1:4" ht="15.5">
-      <c r="A75" s="75"/>
-      <c r="B75" s="78"/>
-      <c r="C75" s="81"/>
+      <c r="A75" s="94"/>
+      <c r="B75" s="88"/>
+      <c r="C75" s="83"/>
       <c r="D75" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15.5">
-      <c r="A76" s="75"/>
-      <c r="B76" s="78"/>
-      <c r="C76" s="81"/>
+      <c r="A76" s="94"/>
+      <c r="B76" s="88"/>
+      <c r="C76" s="83"/>
       <c r="D76" s="28" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15.5">
-      <c r="A77" s="75"/>
-      <c r="B77" s="78"/>
-      <c r="C77" s="81"/>
+      <c r="A77" s="94"/>
+      <c r="B77" s="88"/>
+      <c r="C77" s="83"/>
       <c r="D77" s="28" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15.5">
-      <c r="A78" s="75"/>
-      <c r="B78" s="78"/>
-      <c r="C78" s="81"/>
+      <c r="A78" s="94"/>
+      <c r="B78" s="88"/>
+      <c r="C78" s="83"/>
       <c r="D78" s="28" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15.5">
-      <c r="A79" s="75"/>
-      <c r="B79" s="78"/>
-      <c r="C79" s="81"/>
+      <c r="A79" s="94"/>
+      <c r="B79" s="88"/>
+      <c r="C79" s="83"/>
       <c r="D79" s="28" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15.5">
-      <c r="A80" s="75"/>
-      <c r="B80" s="78"/>
-      <c r="C80" s="81"/>
+      <c r="A80" s="94"/>
+      <c r="B80" s="88"/>
+      <c r="C80" s="83"/>
       <c r="D80" s="28" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15.5">
-      <c r="A81" s="76"/>
-      <c r="B81" s="79"/>
-      <c r="C81" s="82"/>
+      <c r="A81" s="95"/>
+      <c r="B81" s="89"/>
+      <c r="C81" s="84"/>
       <c r="D81" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15.5">
-      <c r="A82" s="74">
+      <c r="A82" s="93">
         <v>6</v>
       </c>
-      <c r="B82" s="77" t="s">
+      <c r="B82" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C82" s="80" t="s">
+      <c r="C82" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D82" s="28" t="s">
@@ -8454,57 +8476,57 @@
       </c>
     </row>
     <row r="83" spans="1:4" ht="15.5">
-      <c r="A83" s="75"/>
-      <c r="B83" s="78"/>
-      <c r="C83" s="81"/>
+      <c r="A83" s="94"/>
+      <c r="B83" s="88"/>
+      <c r="C83" s="83"/>
       <c r="D83" s="28" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15.5">
-      <c r="A84" s="75"/>
-      <c r="B84" s="78"/>
-      <c r="C84" s="81"/>
+      <c r="A84" s="94"/>
+      <c r="B84" s="88"/>
+      <c r="C84" s="83"/>
       <c r="D84" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.5">
-      <c r="A85" s="75"/>
-      <c r="B85" s="78"/>
-      <c r="C85" s="81"/>
+      <c r="A85" s="94"/>
+      <c r="B85" s="88"/>
+      <c r="C85" s="83"/>
       <c r="D85" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.5">
-      <c r="A86" s="75"/>
-      <c r="B86" s="78"/>
-      <c r="C86" s="81"/>
+      <c r="A86" s="94"/>
+      <c r="B86" s="88"/>
+      <c r="C86" s="83"/>
       <c r="D86" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.5">
-      <c r="A87" s="75"/>
-      <c r="B87" s="78"/>
-      <c r="C87" s="81"/>
+      <c r="A87" s="94"/>
+      <c r="B87" s="88"/>
+      <c r="C87" s="83"/>
       <c r="D87" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.5">
-      <c r="A88" s="75"/>
-      <c r="B88" s="78"/>
-      <c r="C88" s="82"/>
+      <c r="A88" s="94"/>
+      <c r="B88" s="88"/>
+      <c r="C88" s="84"/>
       <c r="D88" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.5">
-      <c r="A89" s="75"/>
-      <c r="B89" s="78"/>
-      <c r="C89" s="80" t="s">
+      <c r="A89" s="94"/>
+      <c r="B89" s="88"/>
+      <c r="C89" s="82" t="s">
         <v>103</v>
       </c>
       <c r="D89" s="28" t="s">
@@ -8512,25 +8534,25 @@
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.5">
-      <c r="A90" s="75"/>
-      <c r="B90" s="78"/>
-      <c r="C90" s="81"/>
+      <c r="A90" s="94"/>
+      <c r="B90" s="88"/>
+      <c r="C90" s="83"/>
       <c r="D90" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.5">
-      <c r="A91" s="75"/>
-      <c r="B91" s="78"/>
-      <c r="C91" s="82"/>
+      <c r="A91" s="94"/>
+      <c r="B91" s="88"/>
+      <c r="C91" s="84"/>
       <c r="D91" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.5">
-      <c r="A92" s="75"/>
-      <c r="B92" s="78"/>
-      <c r="C92" s="80" t="s">
+      <c r="A92" s="94"/>
+      <c r="B92" s="88"/>
+      <c r="C92" s="82" t="s">
         <v>96</v>
       </c>
       <c r="D92" s="28" t="s">
@@ -8538,29 +8560,29 @@
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.5">
-      <c r="A93" s="75"/>
-      <c r="B93" s="78"/>
-      <c r="C93" s="81"/>
+      <c r="A93" s="94"/>
+      <c r="B93" s="88"/>
+      <c r="C93" s="83"/>
       <c r="D93" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.5">
-      <c r="A94" s="76"/>
-      <c r="B94" s="79"/>
-      <c r="C94" s="82"/>
+      <c r="A94" s="95"/>
+      <c r="B94" s="89"/>
+      <c r="C94" s="84"/>
       <c r="D94" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.5">
-      <c r="A95" s="74">
+      <c r="A95" s="93">
         <v>7</v>
       </c>
-      <c r="B95" s="77" t="s">
+      <c r="B95" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="C95" s="80" t="s">
+      <c r="C95" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D95" s="28" t="s">
@@ -8568,57 +8590,57 @@
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.5">
-      <c r="A96" s="75"/>
-      <c r="B96" s="78"/>
-      <c r="C96" s="81"/>
+      <c r="A96" s="94"/>
+      <c r="B96" s="88"/>
+      <c r="C96" s="83"/>
       <c r="D96" s="28" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.5">
-      <c r="A97" s="75"/>
-      <c r="B97" s="78"/>
-      <c r="C97" s="81"/>
+      <c r="A97" s="94"/>
+      <c r="B97" s="88"/>
+      <c r="C97" s="83"/>
       <c r="D97" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.5">
-      <c r="A98" s="75"/>
-      <c r="B98" s="78"/>
-      <c r="C98" s="81"/>
+      <c r="A98" s="94"/>
+      <c r="B98" s="88"/>
+      <c r="C98" s="83"/>
       <c r="D98" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.5">
-      <c r="A99" s="75"/>
-      <c r="B99" s="78"/>
-      <c r="C99" s="81"/>
+      <c r="A99" s="94"/>
+      <c r="B99" s="88"/>
+      <c r="C99" s="83"/>
       <c r="D99" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.5">
-      <c r="A100" s="75"/>
-      <c r="B100" s="78"/>
-      <c r="C100" s="81"/>
+      <c r="A100" s="94"/>
+      <c r="B100" s="88"/>
+      <c r="C100" s="83"/>
       <c r="D100" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.5">
-      <c r="A101" s="75"/>
-      <c r="B101" s="78"/>
-      <c r="C101" s="82"/>
+      <c r="A101" s="94"/>
+      <c r="B101" s="88"/>
+      <c r="C101" s="84"/>
       <c r="D101" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.5">
-      <c r="A102" s="75"/>
-      <c r="B102" s="78"/>
-      <c r="C102" s="80" t="s">
+      <c r="A102" s="94"/>
+      <c r="B102" s="88"/>
+      <c r="C102" s="82" t="s">
         <v>103</v>
       </c>
       <c r="D102" s="28" t="s">
@@ -8626,25 +8648,25 @@
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.5">
-      <c r="A103" s="75"/>
-      <c r="B103" s="78"/>
-      <c r="C103" s="81"/>
+      <c r="A103" s="94"/>
+      <c r="B103" s="88"/>
+      <c r="C103" s="83"/>
       <c r="D103" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.5">
-      <c r="A104" s="75"/>
-      <c r="B104" s="78"/>
-      <c r="C104" s="82"/>
+      <c r="A104" s="94"/>
+      <c r="B104" s="88"/>
+      <c r="C104" s="84"/>
       <c r="D104" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.5">
-      <c r="A105" s="75"/>
-      <c r="B105" s="78"/>
-      <c r="C105" s="80" t="s">
+      <c r="A105" s="94"/>
+      <c r="B105" s="88"/>
+      <c r="C105" s="82" t="s">
         <v>96</v>
       </c>
       <c r="D105" s="28" t="s">
@@ -8652,29 +8674,29 @@
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.5">
-      <c r="A106" s="75"/>
-      <c r="B106" s="78"/>
-      <c r="C106" s="81"/>
+      <c r="A106" s="94"/>
+      <c r="B106" s="88"/>
+      <c r="C106" s="83"/>
       <c r="D106" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.5">
-      <c r="A107" s="76"/>
-      <c r="B107" s="79"/>
-      <c r="C107" s="82"/>
+      <c r="A107" s="95"/>
+      <c r="B107" s="89"/>
+      <c r="C107" s="84"/>
       <c r="D107" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.5">
-      <c r="A108" s="74">
+      <c r="A108" s="93">
         <v>8</v>
       </c>
-      <c r="B108" s="77" t="s">
+      <c r="B108" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="C108" s="80" t="s">
+      <c r="C108" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D108" s="28" t="s">
@@ -8682,57 +8704,57 @@
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.5">
-      <c r="A109" s="75"/>
-      <c r="B109" s="78"/>
-      <c r="C109" s="81"/>
+      <c r="A109" s="94"/>
+      <c r="B109" s="88"/>
+      <c r="C109" s="83"/>
       <c r="D109" s="28" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.5">
-      <c r="A110" s="75"/>
-      <c r="B110" s="78"/>
-      <c r="C110" s="81"/>
+      <c r="A110" s="94"/>
+      <c r="B110" s="88"/>
+      <c r="C110" s="83"/>
       <c r="D110" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.5">
-      <c r="A111" s="75"/>
-      <c r="B111" s="78"/>
-      <c r="C111" s="81"/>
+      <c r="A111" s="94"/>
+      <c r="B111" s="88"/>
+      <c r="C111" s="83"/>
       <c r="D111" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.5">
-      <c r="A112" s="75"/>
-      <c r="B112" s="78"/>
-      <c r="C112" s="81"/>
+      <c r="A112" s="94"/>
+      <c r="B112" s="88"/>
+      <c r="C112" s="83"/>
       <c r="D112" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.5">
-      <c r="A113" s="75"/>
-      <c r="B113" s="78"/>
-      <c r="C113" s="81"/>
+      <c r="A113" s="94"/>
+      <c r="B113" s="88"/>
+      <c r="C113" s="83"/>
       <c r="D113" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.5">
-      <c r="A114" s="75"/>
-      <c r="B114" s="78"/>
-      <c r="C114" s="82"/>
+      <c r="A114" s="94"/>
+      <c r="B114" s="88"/>
+      <c r="C114" s="84"/>
       <c r="D114" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.5">
-      <c r="A115" s="75"/>
-      <c r="B115" s="78"/>
-      <c r="C115" s="80" t="s">
+      <c r="A115" s="94"/>
+      <c r="B115" s="88"/>
+      <c r="C115" s="82" t="s">
         <v>103</v>
       </c>
       <c r="D115" s="28" t="s">
@@ -8740,25 +8762,25 @@
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.5">
-      <c r="A116" s="75"/>
-      <c r="B116" s="78"/>
-      <c r="C116" s="81"/>
+      <c r="A116" s="94"/>
+      <c r="B116" s="88"/>
+      <c r="C116" s="83"/>
       <c r="D116" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.5">
-      <c r="A117" s="75"/>
-      <c r="B117" s="78"/>
-      <c r="C117" s="82"/>
+      <c r="A117" s="94"/>
+      <c r="B117" s="88"/>
+      <c r="C117" s="84"/>
       <c r="D117" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.5">
-      <c r="A118" s="75"/>
-      <c r="B118" s="78"/>
-      <c r="C118" s="80" t="s">
+      <c r="A118" s="94"/>
+      <c r="B118" s="88"/>
+      <c r="C118" s="82" t="s">
         <v>96</v>
       </c>
       <c r="D118" s="28" t="s">
@@ -8766,29 +8788,29 @@
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.5">
-      <c r="A119" s="75"/>
-      <c r="B119" s="78"/>
-      <c r="C119" s="81"/>
+      <c r="A119" s="94"/>
+      <c r="B119" s="88"/>
+      <c r="C119" s="83"/>
       <c r="D119" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.5">
-      <c r="A120" s="76"/>
-      <c r="B120" s="79"/>
-      <c r="C120" s="82"/>
+      <c r="A120" s="95"/>
+      <c r="B120" s="89"/>
+      <c r="C120" s="84"/>
       <c r="D120" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.5">
-      <c r="A121" s="74">
+      <c r="A121" s="93">
         <v>9</v>
       </c>
-      <c r="B121" s="77" t="s">
+      <c r="B121" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="C121" s="80" t="s">
+      <c r="C121" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D121" s="28" t="s">
@@ -8796,57 +8818,57 @@
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.5">
-      <c r="A122" s="75"/>
-      <c r="B122" s="78"/>
-      <c r="C122" s="81"/>
+      <c r="A122" s="94"/>
+      <c r="B122" s="88"/>
+      <c r="C122" s="83"/>
       <c r="D122" s="28" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.5">
-      <c r="A123" s="75"/>
-      <c r="B123" s="78"/>
-      <c r="C123" s="81"/>
+      <c r="A123" s="94"/>
+      <c r="B123" s="88"/>
+      <c r="C123" s="83"/>
       <c r="D123" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.5">
-      <c r="A124" s="75"/>
-      <c r="B124" s="78"/>
-      <c r="C124" s="81"/>
+      <c r="A124" s="94"/>
+      <c r="B124" s="88"/>
+      <c r="C124" s="83"/>
       <c r="D124" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.5">
-      <c r="A125" s="75"/>
-      <c r="B125" s="78"/>
-      <c r="C125" s="81"/>
+      <c r="A125" s="94"/>
+      <c r="B125" s="88"/>
+      <c r="C125" s="83"/>
       <c r="D125" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15.5">
-      <c r="A126" s="75"/>
-      <c r="B126" s="78"/>
-      <c r="C126" s="81"/>
+      <c r="A126" s="94"/>
+      <c r="B126" s="88"/>
+      <c r="C126" s="83"/>
       <c r="D126" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.5">
-      <c r="A127" s="75"/>
-      <c r="B127" s="78"/>
-      <c r="C127" s="82"/>
+      <c r="A127" s="94"/>
+      <c r="B127" s="88"/>
+      <c r="C127" s="84"/>
       <c r="D127" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.5">
-      <c r="A128" s="75"/>
-      <c r="B128" s="78"/>
-      <c r="C128" s="80" t="s">
+      <c r="A128" s="94"/>
+      <c r="B128" s="88"/>
+      <c r="C128" s="82" t="s">
         <v>103</v>
       </c>
       <c r="D128" s="28" t="s">
@@ -8854,25 +8876,25 @@
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.5">
-      <c r="A129" s="75"/>
-      <c r="B129" s="78"/>
-      <c r="C129" s="81"/>
+      <c r="A129" s="94"/>
+      <c r="B129" s="88"/>
+      <c r="C129" s="83"/>
       <c r="D129" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.5">
-      <c r="A130" s="75"/>
-      <c r="B130" s="78"/>
-      <c r="C130" s="82"/>
+      <c r="A130" s="94"/>
+      <c r="B130" s="88"/>
+      <c r="C130" s="84"/>
       <c r="D130" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.5">
-      <c r="A131" s="75"/>
-      <c r="B131" s="78"/>
-      <c r="C131" s="80" t="s">
+      <c r="A131" s="94"/>
+      <c r="B131" s="88"/>
+      <c r="C131" s="82" t="s">
         <v>96</v>
       </c>
       <c r="D131" s="28" t="s">
@@ -8880,28 +8902,28 @@
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.5">
-      <c r="A132" s="75"/>
-      <c r="B132" s="78"/>
-      <c r="C132" s="81"/>
+      <c r="A132" s="94"/>
+      <c r="B132" s="88"/>
+      <c r="C132" s="83"/>
       <c r="D132" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.5">
-      <c r="A133" s="76"/>
-      <c r="B133" s="79"/>
-      <c r="C133" s="82"/>
+      <c r="A133" s="95"/>
+      <c r="B133" s="89"/>
+      <c r="C133" s="84"/>
       <c r="D133" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15">
-      <c r="A134" s="89" t="s">
+      <c r="A134" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="B134" s="90"/>
-      <c r="C134" s="90"/>
-      <c r="D134" s="91"/>
+      <c r="B134" s="91"/>
+      <c r="C134" s="91"/>
+      <c r="D134" s="92"/>
     </row>
     <row r="135" spans="1:4" ht="15.5">
       <c r="A135" s="27" t="s">
@@ -8928,13 +8950,13 @@
       <c r="D136" s="33"/>
     </row>
     <row r="137" spans="1:4" ht="15.5">
-      <c r="A137" s="92" t="s">
+      <c r="A137" s="79" t="s">
         <v>119</v>
       </c>
-      <c r="B137" s="77" t="s">
+      <c r="B137" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="C137" s="80" t="s">
+      <c r="C137" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D137" s="28" t="s">
@@ -8942,57 +8964,57 @@
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.5">
-      <c r="A138" s="93"/>
-      <c r="B138" s="78"/>
-      <c r="C138" s="81"/>
+      <c r="A138" s="80"/>
+      <c r="B138" s="88"/>
+      <c r="C138" s="83"/>
       <c r="D138" s="28" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.5">
-      <c r="A139" s="93"/>
-      <c r="B139" s="78"/>
-      <c r="C139" s="81"/>
+      <c r="A139" s="80"/>
+      <c r="B139" s="88"/>
+      <c r="C139" s="83"/>
       <c r="D139" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.5">
-      <c r="A140" s="93"/>
-      <c r="B140" s="78"/>
-      <c r="C140" s="81"/>
+      <c r="A140" s="80"/>
+      <c r="B140" s="88"/>
+      <c r="C140" s="83"/>
       <c r="D140" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.5">
-      <c r="A141" s="93"/>
-      <c r="B141" s="78"/>
-      <c r="C141" s="81"/>
+      <c r="A141" s="80"/>
+      <c r="B141" s="88"/>
+      <c r="C141" s="83"/>
       <c r="D141" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.5">
-      <c r="A142" s="93"/>
-      <c r="B142" s="78"/>
-      <c r="C142" s="81"/>
+      <c r="A142" s="80"/>
+      <c r="B142" s="88"/>
+      <c r="C142" s="83"/>
       <c r="D142" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.5">
-      <c r="A143" s="93"/>
-      <c r="B143" s="78"/>
-      <c r="C143" s="82"/>
+      <c r="A143" s="80"/>
+      <c r="B143" s="88"/>
+      <c r="C143" s="84"/>
       <c r="D143" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.5">
-      <c r="A144" s="93"/>
-      <c r="B144" s="78"/>
-      <c r="C144" s="80" t="s">
+      <c r="A144" s="80"/>
+      <c r="B144" s="88"/>
+      <c r="C144" s="82" t="s">
         <v>103</v>
       </c>
       <c r="D144" s="28" t="s">
@@ -9000,25 +9022,25 @@
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.5">
-      <c r="A145" s="93"/>
-      <c r="B145" s="78"/>
-      <c r="C145" s="81"/>
+      <c r="A145" s="80"/>
+      <c r="B145" s="88"/>
+      <c r="C145" s="83"/>
       <c r="D145" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.5">
-      <c r="A146" s="93"/>
-      <c r="B146" s="78"/>
-      <c r="C146" s="82"/>
+      <c r="A146" s="80"/>
+      <c r="B146" s="88"/>
+      <c r="C146" s="84"/>
       <c r="D146" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.5">
-      <c r="A147" s="93"/>
-      <c r="B147" s="78"/>
-      <c r="C147" s="80" t="s">
+      <c r="A147" s="80"/>
+      <c r="B147" s="88"/>
+      <c r="C147" s="82" t="s">
         <v>96</v>
       </c>
       <c r="D147" s="28" t="s">
@@ -9026,29 +9048,29 @@
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.5">
-      <c r="A148" s="93"/>
-      <c r="B148" s="78"/>
-      <c r="C148" s="81"/>
+      <c r="A148" s="80"/>
+      <c r="B148" s="88"/>
+      <c r="C148" s="83"/>
       <c r="D148" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.5">
-      <c r="A149" s="94"/>
-      <c r="B149" s="79"/>
-      <c r="C149" s="82"/>
+      <c r="A149" s="81"/>
+      <c r="B149" s="89"/>
+      <c r="C149" s="84"/>
       <c r="D149" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.5">
-      <c r="A150" s="92" t="s">
+      <c r="A150" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="B150" s="77" t="s">
+      <c r="B150" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="C150" s="80" t="s">
+      <c r="C150" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D150" s="28" t="s">
@@ -9056,65 +9078,65 @@
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.5">
-      <c r="A151" s="93"/>
-      <c r="B151" s="78"/>
-      <c r="C151" s="81"/>
+      <c r="A151" s="80"/>
+      <c r="B151" s="88"/>
+      <c r="C151" s="83"/>
       <c r="D151" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.5">
-      <c r="A152" s="93"/>
-      <c r="B152" s="78"/>
-      <c r="C152" s="81"/>
+      <c r="A152" s="80"/>
+      <c r="B152" s="88"/>
+      <c r="C152" s="83"/>
       <c r="D152" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.5">
-      <c r="A153" s="93"/>
-      <c r="B153" s="78"/>
-      <c r="C153" s="81"/>
+      <c r="A153" s="80"/>
+      <c r="B153" s="88"/>
+      <c r="C153" s="83"/>
       <c r="D153" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.5">
-      <c r="A154" s="93"/>
-      <c r="B154" s="78"/>
-      <c r="C154" s="81"/>
+      <c r="A154" s="80"/>
+      <c r="B154" s="88"/>
+      <c r="C154" s="83"/>
       <c r="D154" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.5">
-      <c r="A155" s="93"/>
-      <c r="B155" s="78"/>
-      <c r="C155" s="81"/>
+      <c r="A155" s="80"/>
+      <c r="B155" s="88"/>
+      <c r="C155" s="83"/>
       <c r="D155" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.5">
-      <c r="A156" s="93"/>
-      <c r="B156" s="78"/>
-      <c r="C156" s="81"/>
+      <c r="A156" s="80"/>
+      <c r="B156" s="88"/>
+      <c r="C156" s="83"/>
       <c r="D156" s="28" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.5">
-      <c r="A157" s="93"/>
-      <c r="B157" s="78"/>
-      <c r="C157" s="82"/>
+      <c r="A157" s="80"/>
+      <c r="B157" s="88"/>
+      <c r="C157" s="84"/>
       <c r="D157" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.5">
-      <c r="A158" s="93"/>
-      <c r="B158" s="78"/>
-      <c r="C158" s="95" t="s">
+      <c r="A158" s="80"/>
+      <c r="B158" s="88"/>
+      <c r="C158" s="85" t="s">
         <v>103</v>
       </c>
       <c r="D158" s="28" t="s">
@@ -9122,21 +9144,21 @@
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.5">
-      <c r="A159" s="94"/>
-      <c r="B159" s="79"/>
-      <c r="C159" s="96"/>
+      <c r="A159" s="81"/>
+      <c r="B159" s="89"/>
+      <c r="C159" s="86"/>
       <c r="D159" s="28" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.5">
-      <c r="A160" s="92" t="s">
+      <c r="A160" s="79" t="s">
         <v>127</v>
       </c>
-      <c r="B160" s="77" t="s">
+      <c r="B160" s="87" t="s">
         <v>128</v>
       </c>
-      <c r="C160" s="80" t="s">
+      <c r="C160" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D160" s="28" t="s">
@@ -9144,37 +9166,37 @@
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.5">
-      <c r="A161" s="93"/>
-      <c r="B161" s="78"/>
-      <c r="C161" s="81"/>
+      <c r="A161" s="80"/>
+      <c r="B161" s="88"/>
+      <c r="C161" s="83"/>
       <c r="D161" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.5">
-      <c r="A162" s="93"/>
-      <c r="B162" s="78"/>
-      <c r="C162" s="81"/>
+      <c r="A162" s="80"/>
+      <c r="B162" s="88"/>
+      <c r="C162" s="83"/>
       <c r="D162" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.5">
-      <c r="A163" s="94"/>
-      <c r="B163" s="79"/>
-      <c r="C163" s="82"/>
+      <c r="A163" s="81"/>
+      <c r="B163" s="89"/>
+      <c r="C163" s="84"/>
       <c r="D163" s="28" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.5">
-      <c r="A164" s="92" t="s">
+      <c r="A164" s="79" t="s">
         <v>129</v>
       </c>
-      <c r="B164" s="77" t="s">
+      <c r="B164" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="C164" s="80" t="s">
+      <c r="C164" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D164" s="28" t="s">
@@ -9182,61 +9204,61 @@
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.5">
-      <c r="A165" s="93"/>
-      <c r="B165" s="78"/>
-      <c r="C165" s="81"/>
+      <c r="A165" s="80"/>
+      <c r="B165" s="88"/>
+      <c r="C165" s="83"/>
       <c r="D165" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.5">
-      <c r="A166" s="93"/>
-      <c r="B166" s="78"/>
-      <c r="C166" s="81"/>
+      <c r="A166" s="80"/>
+      <c r="B166" s="88"/>
+      <c r="C166" s="83"/>
       <c r="D166" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.5">
-      <c r="A167" s="93"/>
-      <c r="B167" s="78"/>
-      <c r="C167" s="81"/>
+      <c r="A167" s="80"/>
+      <c r="B167" s="88"/>
+      <c r="C167" s="83"/>
       <c r="D167" s="28" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.5">
-      <c r="A168" s="93"/>
-      <c r="B168" s="78"/>
-      <c r="C168" s="81"/>
+      <c r="A168" s="80"/>
+      <c r="B168" s="88"/>
+      <c r="C168" s="83"/>
       <c r="D168" s="28" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.5">
-      <c r="A169" s="93"/>
-      <c r="B169" s="78"/>
-      <c r="C169" s="81"/>
+      <c r="A169" s="80"/>
+      <c r="B169" s="88"/>
+      <c r="C169" s="83"/>
       <c r="D169" s="28" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.5">
-      <c r="A170" s="94"/>
-      <c r="B170" s="79"/>
-      <c r="C170" s="82"/>
+      <c r="A170" s="81"/>
+      <c r="B170" s="89"/>
+      <c r="C170" s="84"/>
       <c r="D170" s="28" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.5">
-      <c r="A171" s="92" t="s">
+      <c r="A171" s="79" t="s">
         <v>131</v>
       </c>
-      <c r="B171" s="77" t="s">
+      <c r="B171" s="87" t="s">
         <v>132</v>
       </c>
-      <c r="C171" s="80" t="s">
+      <c r="C171" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D171" s="28" t="s">
@@ -9244,73 +9266,73 @@
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.5">
-      <c r="A172" s="93"/>
-      <c r="B172" s="78"/>
-      <c r="C172" s="81"/>
+      <c r="A172" s="80"/>
+      <c r="B172" s="88"/>
+      <c r="C172" s="83"/>
       <c r="D172" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.5">
-      <c r="A173" s="93"/>
-      <c r="B173" s="78"/>
-      <c r="C173" s="81"/>
+      <c r="A173" s="80"/>
+      <c r="B173" s="88"/>
+      <c r="C173" s="83"/>
       <c r="D173" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.5">
-      <c r="A174" s="93"/>
-      <c r="B174" s="78"/>
-      <c r="C174" s="81"/>
+      <c r="A174" s="80"/>
+      <c r="B174" s="88"/>
+      <c r="C174" s="83"/>
       <c r="D174" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.5">
-      <c r="A175" s="93"/>
-      <c r="B175" s="78"/>
-      <c r="C175" s="81"/>
+      <c r="A175" s="80"/>
+      <c r="B175" s="88"/>
+      <c r="C175" s="83"/>
       <c r="D175" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.5">
-      <c r="A176" s="93"/>
-      <c r="B176" s="78"/>
-      <c r="C176" s="81"/>
+      <c r="A176" s="80"/>
+      <c r="B176" s="88"/>
+      <c r="C176" s="83"/>
       <c r="D176" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.5">
-      <c r="A177" s="93"/>
-      <c r="B177" s="78"/>
-      <c r="C177" s="81"/>
+      <c r="A177" s="80"/>
+      <c r="B177" s="88"/>
+      <c r="C177" s="83"/>
       <c r="D177" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.5">
-      <c r="A178" s="93"/>
-      <c r="B178" s="78"/>
-      <c r="C178" s="81"/>
+      <c r="A178" s="80"/>
+      <c r="B178" s="88"/>
+      <c r="C178" s="83"/>
       <c r="D178" s="28" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.5">
-      <c r="A179" s="93"/>
-      <c r="B179" s="78"/>
-      <c r="C179" s="82"/>
+      <c r="A179" s="80"/>
+      <c r="B179" s="88"/>
+      <c r="C179" s="84"/>
       <c r="D179" s="32" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.5">
-      <c r="A180" s="93"/>
-      <c r="B180" s="78"/>
-      <c r="C180" s="95" t="s">
+      <c r="A180" s="80"/>
+      <c r="B180" s="88"/>
+      <c r="C180" s="85" t="s">
         <v>103</v>
       </c>
       <c r="D180" s="28" t="s">
@@ -9318,9 +9340,9 @@
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.5">
-      <c r="A181" s="94"/>
-      <c r="B181" s="79"/>
-      <c r="C181" s="96"/>
+      <c r="A181" s="81"/>
+      <c r="B181" s="89"/>
+      <c r="C181" s="86"/>
       <c r="D181" s="28" t="s">
         <v>126</v>
       </c>
@@ -9336,13 +9358,13 @@
       <c r="D182" s="33"/>
     </row>
     <row r="183" spans="1:4" ht="15.5">
-      <c r="A183" s="92" t="s">
+      <c r="A183" s="79" t="s">
         <v>170</v>
       </c>
-      <c r="B183" s="92" t="s">
+      <c r="B183" s="79" t="s">
         <v>171</v>
       </c>
-      <c r="C183" s="80" t="s">
+      <c r="C183" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D183" s="28" t="s">
@@ -9350,65 +9372,65 @@
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.5">
-      <c r="A184" s="93"/>
-      <c r="B184" s="93"/>
-      <c r="C184" s="81"/>
+      <c r="A184" s="80"/>
+      <c r="B184" s="80"/>
+      <c r="C184" s="83"/>
       <c r="D184" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.5">
-      <c r="A185" s="93"/>
-      <c r="B185" s="93"/>
-      <c r="C185" s="81"/>
+      <c r="A185" s="80"/>
+      <c r="B185" s="80"/>
+      <c r="C185" s="83"/>
       <c r="D185" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.5">
-      <c r="A186" s="93"/>
-      <c r="B186" s="93"/>
-      <c r="C186" s="81"/>
+      <c r="A186" s="80"/>
+      <c r="B186" s="80"/>
+      <c r="C186" s="83"/>
       <c r="D186" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.5">
-      <c r="A187" s="93"/>
-      <c r="B187" s="93"/>
-      <c r="C187" s="81"/>
+      <c r="A187" s="80"/>
+      <c r="B187" s="80"/>
+      <c r="C187" s="83"/>
       <c r="D187" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.5">
-      <c r="A188" s="93"/>
-      <c r="B188" s="93"/>
-      <c r="C188" s="81"/>
+      <c r="A188" s="80"/>
+      <c r="B188" s="80"/>
+      <c r="C188" s="83"/>
       <c r="D188" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.5">
-      <c r="A189" s="93"/>
-      <c r="B189" s="93"/>
-      <c r="C189" s="81"/>
+      <c r="A189" s="80"/>
+      <c r="B189" s="80"/>
+      <c r="C189" s="83"/>
       <c r="D189" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.5">
-      <c r="A190" s="93"/>
-      <c r="B190" s="93"/>
-      <c r="C190" s="82"/>
+      <c r="A190" s="80"/>
+      <c r="B190" s="80"/>
+      <c r="C190" s="84"/>
       <c r="D190" s="32" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.5">
-      <c r="A191" s="93"/>
-      <c r="B191" s="93"/>
-      <c r="C191" s="95" t="s">
+      <c r="A191" s="80"/>
+      <c r="B191" s="80"/>
+      <c r="C191" s="85" t="s">
         <v>103</v>
       </c>
       <c r="D191" s="28" t="s">
@@ -9416,26 +9438,26 @@
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.5">
-      <c r="A192" s="93"/>
-      <c r="B192" s="93"/>
-      <c r="C192" s="96"/>
+      <c r="A192" s="80"/>
+      <c r="B192" s="80"/>
+      <c r="C192" s="86"/>
       <c r="D192" s="28" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="193" spans="1:4">
-      <c r="A193" s="94"/>
-      <c r="B193" s="94"/>
+      <c r="A193" s="81"/>
+      <c r="B193" s="81"/>
       <c r="C193" s="33"/>
       <c r="D193" s="33"/>
     </row>
     <row r="194" spans="1:4" ht="15.5">
-      <c r="A194" s="100" t="s">
+      <c r="A194" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="B194" s="101"/>
-      <c r="C194" s="101"/>
-      <c r="D194" s="102"/>
+      <c r="B194" s="76"/>
+      <c r="C194" s="76"/>
+      <c r="D194" s="77"/>
     </row>
     <row r="195" spans="1:4" ht="15.5">
       <c r="A195" s="27" t="s">
@@ -9452,13 +9474,13 @@
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.5">
-      <c r="A196" s="92" t="s">
+      <c r="A196" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="B196" s="77" t="s">
+      <c r="B196" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="C196" s="80" t="s">
+      <c r="C196" s="82" t="s">
         <v>95</v>
       </c>
       <c r="D196" s="28" t="s">
@@ -9466,65 +9488,65 @@
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.5">
-      <c r="A197" s="93"/>
-      <c r="B197" s="78"/>
-      <c r="C197" s="81"/>
+      <c r="A197" s="80"/>
+      <c r="B197" s="88"/>
+      <c r="C197" s="83"/>
       <c r="D197" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.5">
-      <c r="A198" s="93"/>
-      <c r="B198" s="78"/>
-      <c r="C198" s="81"/>
+      <c r="A198" s="80"/>
+      <c r="B198" s="88"/>
+      <c r="C198" s="83"/>
       <c r="D198" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.5">
-      <c r="A199" s="93"/>
-      <c r="B199" s="78"/>
-      <c r="C199" s="81"/>
+      <c r="A199" s="80"/>
+      <c r="B199" s="88"/>
+      <c r="C199" s="83"/>
       <c r="D199" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.5">
-      <c r="A200" s="93"/>
-      <c r="B200" s="78"/>
-      <c r="C200" s="81"/>
+      <c r="A200" s="80"/>
+      <c r="B200" s="88"/>
+      <c r="C200" s="83"/>
       <c r="D200" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15.5">
-      <c r="A201" s="93"/>
-      <c r="B201" s="78"/>
-      <c r="C201" s="81"/>
+      <c r="A201" s="80"/>
+      <c r="B201" s="88"/>
+      <c r="C201" s="83"/>
       <c r="D201" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.5">
-      <c r="A202" s="93"/>
-      <c r="B202" s="78"/>
-      <c r="C202" s="81"/>
+      <c r="A202" s="80"/>
+      <c r="B202" s="88"/>
+      <c r="C202" s="83"/>
       <c r="D202" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.5">
-      <c r="A203" s="93"/>
-      <c r="B203" s="78"/>
-      <c r="C203" s="82"/>
+      <c r="A203" s="80"/>
+      <c r="B203" s="88"/>
+      <c r="C203" s="84"/>
       <c r="D203" s="32" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.5">
-      <c r="A204" s="93"/>
-      <c r="B204" s="78"/>
-      <c r="C204" s="95" t="s">
+      <c r="A204" s="80"/>
+      <c r="B204" s="88"/>
+      <c r="C204" s="85" t="s">
         <v>103</v>
       </c>
       <c r="D204" s="28" t="s">
@@ -9532,20 +9554,20 @@
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.5">
-      <c r="A205" s="94"/>
-      <c r="B205" s="79"/>
-      <c r="C205" s="96"/>
+      <c r="A205" s="81"/>
+      <c r="B205" s="89"/>
+      <c r="C205" s="86"/>
       <c r="D205" s="28" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15">
-      <c r="A206" s="97" t="s">
+      <c r="A206" s="72" t="s">
         <v>173</v>
       </c>
-      <c r="B206" s="98"/>
-      <c r="C206" s="98"/>
-      <c r="D206" s="99"/>
+      <c r="B206" s="73"/>
+      <c r="C206" s="73"/>
+      <c r="D206" s="74"/>
     </row>
     <row r="207" spans="1:4" ht="15.5">
       <c r="A207" s="27" t="s">
@@ -9582,12 +9604,12 @@
       <c r="D209" s="34"/>
     </row>
     <row r="210" spans="1:4" ht="15.5">
-      <c r="A210" s="100" t="s">
+      <c r="A210" s="75" t="s">
         <v>135</v>
       </c>
-      <c r="B210" s="101"/>
-      <c r="C210" s="101"/>
-      <c r="D210" s="102"/>
+      <c r="B210" s="76"/>
+      <c r="C210" s="76"/>
+      <c r="D210" s="77"/>
     </row>
     <row r="211" spans="1:4" ht="15.5">
       <c r="A211" s="27" t="s">
@@ -9645,6 +9667,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:A15"/>
+    <mergeCell ref="B3:B15"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="A29:A41"/>
+    <mergeCell ref="B29:B41"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="A16:A28"/>
+    <mergeCell ref="B16:B28"/>
+    <mergeCell ref="C16:C22"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="A59:A81"/>
+    <mergeCell ref="B59:B81"/>
+    <mergeCell ref="C59:C65"/>
+    <mergeCell ref="C66:C73"/>
+    <mergeCell ref="C74:C81"/>
+    <mergeCell ref="A42:A58"/>
+    <mergeCell ref="B42:B58"/>
+    <mergeCell ref="C42:C48"/>
+    <mergeCell ref="C49:C53"/>
+    <mergeCell ref="C54:C58"/>
+    <mergeCell ref="A95:A107"/>
+    <mergeCell ref="B95:B107"/>
+    <mergeCell ref="C95:C101"/>
+    <mergeCell ref="C102:C104"/>
+    <mergeCell ref="C105:C107"/>
+    <mergeCell ref="A82:A94"/>
+    <mergeCell ref="B82:B94"/>
+    <mergeCell ref="C82:C88"/>
+    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="C92:C94"/>
+    <mergeCell ref="A121:A133"/>
+    <mergeCell ref="B121:B133"/>
+    <mergeCell ref="C121:C127"/>
+    <mergeCell ref="C128:C130"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="A108:A120"/>
+    <mergeCell ref="B108:B120"/>
+    <mergeCell ref="C108:C114"/>
+    <mergeCell ref="C115:C117"/>
+    <mergeCell ref="C118:C120"/>
+    <mergeCell ref="A134:D134"/>
+    <mergeCell ref="A137:A149"/>
+    <mergeCell ref="B137:B149"/>
+    <mergeCell ref="C137:C143"/>
+    <mergeCell ref="C144:C146"/>
+    <mergeCell ref="C147:C149"/>
+    <mergeCell ref="B171:B181"/>
+    <mergeCell ref="C171:C179"/>
+    <mergeCell ref="C180:C181"/>
+    <mergeCell ref="A150:A159"/>
+    <mergeCell ref="B150:B159"/>
+    <mergeCell ref="C150:C157"/>
+    <mergeCell ref="C158:C159"/>
+    <mergeCell ref="A160:A163"/>
+    <mergeCell ref="B160:B163"/>
+    <mergeCell ref="C160:C163"/>
     <mergeCell ref="A206:D206"/>
     <mergeCell ref="A210:D210"/>
     <mergeCell ref="E1:E3"/>
@@ -9661,68 +9745,6 @@
     <mergeCell ref="B164:B170"/>
     <mergeCell ref="C164:C170"/>
     <mergeCell ref="A171:A181"/>
-    <mergeCell ref="B171:B181"/>
-    <mergeCell ref="C171:C179"/>
-    <mergeCell ref="C180:C181"/>
-    <mergeCell ref="A150:A159"/>
-    <mergeCell ref="B150:B159"/>
-    <mergeCell ref="C150:C157"/>
-    <mergeCell ref="C158:C159"/>
-    <mergeCell ref="A160:A163"/>
-    <mergeCell ref="B160:B163"/>
-    <mergeCell ref="C160:C163"/>
-    <mergeCell ref="A134:D134"/>
-    <mergeCell ref="A137:A149"/>
-    <mergeCell ref="B137:B149"/>
-    <mergeCell ref="C137:C143"/>
-    <mergeCell ref="C144:C146"/>
-    <mergeCell ref="C147:C149"/>
-    <mergeCell ref="A108:A120"/>
-    <mergeCell ref="B108:B120"/>
-    <mergeCell ref="C108:C114"/>
-    <mergeCell ref="C115:C117"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="A121:A133"/>
-    <mergeCell ref="B121:B133"/>
-    <mergeCell ref="C121:C127"/>
-    <mergeCell ref="C128:C130"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="A82:A94"/>
-    <mergeCell ref="B82:B94"/>
-    <mergeCell ref="C82:C88"/>
-    <mergeCell ref="C89:C91"/>
-    <mergeCell ref="C92:C94"/>
-    <mergeCell ref="A95:A107"/>
-    <mergeCell ref="B95:B107"/>
-    <mergeCell ref="C95:C101"/>
-    <mergeCell ref="C102:C104"/>
-    <mergeCell ref="C105:C107"/>
-    <mergeCell ref="A42:A58"/>
-    <mergeCell ref="B42:B58"/>
-    <mergeCell ref="C42:C48"/>
-    <mergeCell ref="C49:C53"/>
-    <mergeCell ref="C54:C58"/>
-    <mergeCell ref="A59:A81"/>
-    <mergeCell ref="B59:B81"/>
-    <mergeCell ref="C59:C65"/>
-    <mergeCell ref="C66:C73"/>
-    <mergeCell ref="C74:C81"/>
-    <mergeCell ref="A16:A28"/>
-    <mergeCell ref="B16:B28"/>
-    <mergeCell ref="C16:C22"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="A29:A41"/>
-    <mergeCell ref="B29:B41"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:A15"/>
-    <mergeCell ref="B3:B15"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C13:C15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9739,20 +9761,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="31.5" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
     </row>
     <row r="2" spans="1:4" ht="23.5">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
     </row>
     <row r="3" spans="1:4" ht="15.5">
       <c r="A3" s="27" t="s">
@@ -9769,13 +9791,13 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.5">
-      <c r="A4" s="39">
+      <c r="A4" s="51">
         <v>1</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D4" s="28" t="s">
@@ -9783,49 +9805,49 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.5">
-      <c r="A5" s="40"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="43"/>
+      <c r="A5" s="49"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="46"/>
       <c r="D5" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.5">
-      <c r="A6" s="40"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="43"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="46"/>
       <c r="D6" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.5">
-      <c r="A7" s="40"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="43"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="46"/>
       <c r="D7" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.5">
-      <c r="A8" s="40"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="43"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="46"/>
       <c r="D8" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.5">
-      <c r="A9" s="40"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="43"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="46"/>
       <c r="D9" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.5">
-      <c r="A10" s="40"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="42" t="s">
+      <c r="A10" s="49"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D10" s="28" t="s">
@@ -9833,25 +9855,25 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.5">
-      <c r="A11" s="40"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="43"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="46"/>
       <c r="D11" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.5">
-      <c r="A12" s="40"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="43"/>
+      <c r="A12" s="49"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="46"/>
       <c r="D12" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.5">
-      <c r="A13" s="40"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="42" t="s">
+      <c r="A13" s="49"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D13" s="28" t="s">
@@ -9859,29 +9881,29 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.5">
-      <c r="A14" s="40"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="43"/>
+      <c r="A14" s="49"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="46"/>
       <c r="D14" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.5">
-      <c r="A15" s="40"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="43"/>
+      <c r="A15" s="49"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="46"/>
       <c r="D15" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.5">
-      <c r="A16" s="39">
+      <c r="A16" s="51">
         <v>2</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D16" s="28" t="s">
@@ -9889,49 +9911,49 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.5">
-      <c r="A17" s="40"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="43"/>
+      <c r="A17" s="49"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="46"/>
       <c r="D17" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.5">
-      <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="43"/>
+      <c r="A18" s="49"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="46"/>
       <c r="D18" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.5">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="43"/>
+      <c r="A19" s="49"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="46"/>
       <c r="D19" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.5">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="43"/>
+      <c r="A20" s="49"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="46"/>
       <c r="D20" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.5">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="43"/>
+      <c r="A21" s="49"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="46"/>
       <c r="D21" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.5">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="42" t="s">
+      <c r="A22" s="49"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D22" s="28" t="s">
@@ -9939,25 +9961,25 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.5">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="43"/>
+      <c r="A23" s="49"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="46"/>
       <c r="D23" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.5">
-      <c r="A24" s="40"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="43"/>
+      <c r="A24" s="49"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="46"/>
       <c r="D24" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.5">
-      <c r="A25" s="40"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="42" t="s">
+      <c r="A25" s="49"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D25" s="28" t="s">
@@ -9965,29 +9987,29 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.5">
-      <c r="A26" s="40"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="43"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="46"/>
       <c r="D26" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.5">
-      <c r="A27" s="40"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="43"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="46"/>
       <c r="D27" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.5">
-      <c r="A28" s="44">
+      <c r="A28" s="52">
         <v>3</v>
       </c>
-      <c r="B28" s="46" t="s">
+      <c r="B28" s="54" t="s">
         <v>166</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D28" s="28" t="s">
@@ -9995,49 +10017,49 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.5">
-      <c r="A29" s="45"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="43"/>
+      <c r="A29" s="53"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="46"/>
       <c r="D29" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.5">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="43"/>
+      <c r="A30" s="53"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="46"/>
       <c r="D30" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.5">
-      <c r="A31" s="45"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="43"/>
+      <c r="A31" s="53"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="46"/>
       <c r="D31" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.5">
-      <c r="A32" s="45"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="43"/>
+      <c r="A32" s="53"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="46"/>
       <c r="D32" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.5">
-      <c r="A33" s="45"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="43"/>
+      <c r="A33" s="53"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="46"/>
       <c r="D33" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.5">
-      <c r="A34" s="45"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="42" t="s">
+      <c r="A34" s="53"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D34" s="28" t="s">
@@ -10045,25 +10067,25 @@
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.5">
-      <c r="A35" s="45"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="43"/>
+      <c r="A35" s="53"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="46"/>
       <c r="D35" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15.5">
-      <c r="A36" s="45"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="43"/>
+      <c r="A36" s="53"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="46"/>
       <c r="D36" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15.5">
-      <c r="A37" s="45"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="42" t="s">
+      <c r="A37" s="53"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D37" s="28" t="s">
@@ -10071,29 +10093,29 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.5">
-      <c r="A38" s="45"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="43"/>
+      <c r="A38" s="53"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="46"/>
       <c r="D38" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.5">
-      <c r="A39" s="45"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="43"/>
+      <c r="A39" s="53"/>
+      <c r="B39" s="53"/>
+      <c r="C39" s="46"/>
       <c r="D39" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.5">
-      <c r="A40" s="39">
+      <c r="A40" s="51">
         <v>4</v>
       </c>
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="42" t="s">
+      <c r="C40" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D40" s="28" t="s">
@@ -10101,49 +10123,49 @@
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.5">
-      <c r="A41" s="40"/>
-      <c r="B41" s="40"/>
-      <c r="C41" s="43"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="46"/>
       <c r="D41" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.5">
-      <c r="A42" s="40"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="43"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="46"/>
       <c r="D42" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.5">
-      <c r="A43" s="40"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="43"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="46"/>
       <c r="D43" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.5">
-      <c r="A44" s="40"/>
-      <c r="B44" s="40"/>
-      <c r="C44" s="43"/>
+      <c r="A44" s="49"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="46"/>
       <c r="D44" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.5">
-      <c r="A45" s="40"/>
-      <c r="B45" s="40"/>
-      <c r="C45" s="43"/>
+      <c r="A45" s="49"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="46"/>
       <c r="D45" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15.5">
-      <c r="A46" s="40"/>
-      <c r="B46" s="40"/>
-      <c r="C46" s="42" t="s">
+      <c r="A46" s="49"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D46" s="28" t="s">
@@ -10151,41 +10173,41 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.5">
-      <c r="A47" s="40"/>
-      <c r="B47" s="40"/>
-      <c r="C47" s="43"/>
+      <c r="A47" s="49"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="46"/>
       <c r="D47" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.5">
-      <c r="A48" s="40"/>
-      <c r="B48" s="40"/>
-      <c r="C48" s="43"/>
+      <c r="A48" s="49"/>
+      <c r="B48" s="49"/>
+      <c r="C48" s="46"/>
       <c r="D48" s="28" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.5">
-      <c r="A49" s="40"/>
-      <c r="B49" s="40"/>
-      <c r="C49" s="43"/>
+      <c r="A49" s="49"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="46"/>
       <c r="D49" s="28" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15.5">
-      <c r="A50" s="40"/>
-      <c r="B50" s="40"/>
-      <c r="C50" s="43"/>
+      <c r="A50" s="49"/>
+      <c r="B50" s="49"/>
+      <c r="C50" s="46"/>
       <c r="D50" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15.5">
-      <c r="A51" s="40"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="42" t="s">
+      <c r="A51" s="49"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D51" s="28" t="s">
@@ -10193,45 +10215,45 @@
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.5">
-      <c r="A52" s="40"/>
-      <c r="B52" s="40"/>
-      <c r="C52" s="43"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="49"/>
+      <c r="C52" s="46"/>
       <c r="D52" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15.5">
-      <c r="A53" s="40"/>
-      <c r="B53" s="40"/>
-      <c r="C53" s="43"/>
+      <c r="A53" s="49"/>
+      <c r="B53" s="49"/>
+      <c r="C53" s="46"/>
       <c r="D53" s="28" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.5">
-      <c r="A54" s="40"/>
-      <c r="B54" s="40"/>
-      <c r="C54" s="43"/>
+      <c r="A54" s="49"/>
+      <c r="B54" s="49"/>
+      <c r="C54" s="46"/>
       <c r="D54" s="28" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.5">
-      <c r="A55" s="40"/>
-      <c r="B55" s="40"/>
-      <c r="C55" s="43"/>
+      <c r="A55" s="49"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="46"/>
       <c r="D55" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.5">
-      <c r="A56" s="39">
+      <c r="A56" s="51">
         <v>5</v>
       </c>
-      <c r="B56" s="41" t="s">
+      <c r="B56" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="C56" s="42" t="s">
+      <c r="C56" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D56" s="28" t="s">
@@ -10239,49 +10261,49 @@
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.5">
-      <c r="A57" s="40"/>
-      <c r="B57" s="40"/>
-      <c r="C57" s="43"/>
+      <c r="A57" s="49"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="46"/>
       <c r="D57" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15.5">
-      <c r="A58" s="40"/>
-      <c r="B58" s="40"/>
-      <c r="C58" s="43"/>
+      <c r="A58" s="49"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="46"/>
       <c r="D58" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.5">
-      <c r="A59" s="40"/>
-      <c r="B59" s="40"/>
-      <c r="C59" s="43"/>
+      <c r="A59" s="49"/>
+      <c r="B59" s="49"/>
+      <c r="C59" s="46"/>
       <c r="D59" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15.5">
-      <c r="A60" s="40"/>
-      <c r="B60" s="40"/>
-      <c r="C60" s="43"/>
+      <c r="A60" s="49"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="46"/>
       <c r="D60" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.5">
-      <c r="A61" s="40"/>
-      <c r="B61" s="40"/>
-      <c r="C61" s="43"/>
+      <c r="A61" s="49"/>
+      <c r="B61" s="49"/>
+      <c r="C61" s="46"/>
       <c r="D61" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.5">
-      <c r="A62" s="40"/>
-      <c r="B62" s="40"/>
-      <c r="C62" s="42" t="s">
+      <c r="A62" s="49"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D62" s="28" t="s">
@@ -10289,65 +10311,65 @@
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.5">
-      <c r="A63" s="40"/>
-      <c r="B63" s="40"/>
-      <c r="C63" s="43"/>
+      <c r="A63" s="49"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="46"/>
       <c r="D63" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.5">
-      <c r="A64" s="40"/>
-      <c r="B64" s="40"/>
-      <c r="C64" s="43"/>
+      <c r="A64" s="49"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="46"/>
       <c r="D64" s="28" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15.5">
-      <c r="A65" s="40"/>
-      <c r="B65" s="40"/>
-      <c r="C65" s="43"/>
+      <c r="A65" s="49"/>
+      <c r="B65" s="49"/>
+      <c r="C65" s="46"/>
       <c r="D65" s="28" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.5">
-      <c r="A66" s="40"/>
-      <c r="B66" s="40"/>
-      <c r="C66" s="43"/>
+      <c r="A66" s="49"/>
+      <c r="B66" s="49"/>
+      <c r="C66" s="46"/>
       <c r="D66" s="28" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.5">
-      <c r="A67" s="40"/>
-      <c r="B67" s="40"/>
-      <c r="C67" s="43"/>
+      <c r="A67" s="49"/>
+      <c r="B67" s="49"/>
+      <c r="C67" s="46"/>
       <c r="D67" s="28" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.5">
-      <c r="A68" s="40"/>
-      <c r="B68" s="40"/>
-      <c r="C68" s="43"/>
+      <c r="A68" s="49"/>
+      <c r="B68" s="49"/>
+      <c r="C68" s="46"/>
       <c r="D68" s="28" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.5">
-      <c r="A69" s="40"/>
-      <c r="B69" s="40"/>
-      <c r="C69" s="43"/>
+      <c r="A69" s="49"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="46"/>
       <c r="D69" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.5">
-      <c r="A70" s="40"/>
-      <c r="B70" s="40"/>
-      <c r="C70" s="42" t="s">
+      <c r="A70" s="49"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D70" s="28" t="s">
@@ -10355,69 +10377,69 @@
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.5">
-      <c r="A71" s="40"/>
-      <c r="B71" s="40"/>
-      <c r="C71" s="43"/>
+      <c r="A71" s="49"/>
+      <c r="B71" s="49"/>
+      <c r="C71" s="46"/>
       <c r="D71" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.5">
-      <c r="A72" s="40"/>
-      <c r="B72" s="40"/>
-      <c r="C72" s="43"/>
+      <c r="A72" s="49"/>
+      <c r="B72" s="49"/>
+      <c r="C72" s="46"/>
       <c r="D72" s="28" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.5">
-      <c r="A73" s="40"/>
-      <c r="B73" s="40"/>
-      <c r="C73" s="43"/>
+      <c r="A73" s="49"/>
+      <c r="B73" s="49"/>
+      <c r="C73" s="46"/>
       <c r="D73" s="28" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15.5">
-      <c r="A74" s="40"/>
-      <c r="B74" s="40"/>
-      <c r="C74" s="43"/>
+      <c r="A74" s="49"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="46"/>
       <c r="D74" s="28" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15.5">
-      <c r="A75" s="40"/>
-      <c r="B75" s="40"/>
-      <c r="C75" s="43"/>
+      <c r="A75" s="49"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="46"/>
       <c r="D75" s="28" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15.5">
-      <c r="A76" s="40"/>
-      <c r="B76" s="40"/>
-      <c r="C76" s="43"/>
+      <c r="A76" s="49"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="46"/>
       <c r="D76" s="28" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15.5">
-      <c r="A77" s="40"/>
-      <c r="B77" s="40"/>
-      <c r="C77" s="43"/>
+      <c r="A77" s="49"/>
+      <c r="B77" s="49"/>
+      <c r="C77" s="46"/>
       <c r="D77" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15.5">
-      <c r="A78" s="39">
+      <c r="A78" s="51">
         <v>6</v>
       </c>
-      <c r="B78" s="41" t="s">
+      <c r="B78" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="C78" s="42" t="s">
+      <c r="C78" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D78" s="28" t="s">
@@ -10425,49 +10447,49 @@
       </c>
     </row>
     <row r="79" spans="1:4" ht="15.5">
-      <c r="A79" s="40"/>
-      <c r="B79" s="40"/>
-      <c r="C79" s="43"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="46"/>
       <c r="D79" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15.5">
-      <c r="A80" s="40"/>
-      <c r="B80" s="40"/>
-      <c r="C80" s="43"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="46"/>
       <c r="D80" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15.5">
-      <c r="A81" s="40"/>
-      <c r="B81" s="40"/>
-      <c r="C81" s="43"/>
+      <c r="A81" s="49"/>
+      <c r="B81" s="49"/>
+      <c r="C81" s="46"/>
       <c r="D81" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15.5">
-      <c r="A82" s="40"/>
-      <c r="B82" s="40"/>
-      <c r="C82" s="43"/>
+      <c r="A82" s="49"/>
+      <c r="B82" s="49"/>
+      <c r="C82" s="46"/>
       <c r="D82" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15.5">
-      <c r="A83" s="40"/>
-      <c r="B83" s="40"/>
-      <c r="C83" s="43"/>
+      <c r="A83" s="49"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="46"/>
       <c r="D83" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15.5">
-      <c r="A84" s="40"/>
-      <c r="B84" s="40"/>
-      <c r="C84" s="42" t="s">
+      <c r="A84" s="49"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D84" s="28" t="s">
@@ -10475,25 +10497,25 @@
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.5">
-      <c r="A85" s="40"/>
-      <c r="B85" s="40"/>
-      <c r="C85" s="43"/>
+      <c r="A85" s="49"/>
+      <c r="B85" s="49"/>
+      <c r="C85" s="46"/>
       <c r="D85" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.5">
-      <c r="A86" s="40"/>
-      <c r="B86" s="40"/>
-      <c r="C86" s="43"/>
+      <c r="A86" s="49"/>
+      <c r="B86" s="49"/>
+      <c r="C86" s="46"/>
       <c r="D86" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.5">
-      <c r="A87" s="40"/>
-      <c r="B87" s="40"/>
-      <c r="C87" s="42" t="s">
+      <c r="A87" s="49"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D87" s="28" t="s">
@@ -10501,29 +10523,29 @@
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.5">
-      <c r="A88" s="40"/>
-      <c r="B88" s="40"/>
-      <c r="C88" s="43"/>
+      <c r="A88" s="49"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="46"/>
       <c r="D88" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.5">
-      <c r="A89" s="40"/>
-      <c r="B89" s="40"/>
-      <c r="C89" s="43"/>
+      <c r="A89" s="49"/>
+      <c r="B89" s="49"/>
+      <c r="C89" s="46"/>
       <c r="D89" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.5">
-      <c r="A90" s="39">
+      <c r="A90" s="51">
         <v>7</v>
       </c>
-      <c r="B90" s="41" t="s">
+      <c r="B90" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="C90" s="42" t="s">
+      <c r="C90" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D90" s="28" t="s">
@@ -10531,49 +10553,49 @@
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.5">
-      <c r="A91" s="40"/>
-      <c r="B91" s="40"/>
-      <c r="C91" s="43"/>
+      <c r="A91" s="49"/>
+      <c r="B91" s="49"/>
+      <c r="C91" s="46"/>
       <c r="D91" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.5">
-      <c r="A92" s="40"/>
-      <c r="B92" s="40"/>
-      <c r="C92" s="43"/>
+      <c r="A92" s="49"/>
+      <c r="B92" s="49"/>
+      <c r="C92" s="46"/>
       <c r="D92" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.5">
-      <c r="A93" s="40"/>
-      <c r="B93" s="40"/>
-      <c r="C93" s="43"/>
+      <c r="A93" s="49"/>
+      <c r="B93" s="49"/>
+      <c r="C93" s="46"/>
       <c r="D93" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.5">
-      <c r="A94" s="40"/>
-      <c r="B94" s="40"/>
-      <c r="C94" s="43"/>
+      <c r="A94" s="49"/>
+      <c r="B94" s="49"/>
+      <c r="C94" s="46"/>
       <c r="D94" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.5">
-      <c r="A95" s="40"/>
-      <c r="B95" s="40"/>
-      <c r="C95" s="43"/>
+      <c r="A95" s="49"/>
+      <c r="B95" s="49"/>
+      <c r="C95" s="46"/>
       <c r="D95" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.5">
-      <c r="A96" s="40"/>
-      <c r="B96" s="40"/>
-      <c r="C96" s="42" t="s">
+      <c r="A96" s="49"/>
+      <c r="B96" s="49"/>
+      <c r="C96" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D96" s="28" t="s">
@@ -10581,25 +10603,25 @@
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.5">
-      <c r="A97" s="40"/>
-      <c r="B97" s="40"/>
-      <c r="C97" s="43"/>
+      <c r="A97" s="49"/>
+      <c r="B97" s="49"/>
+      <c r="C97" s="46"/>
       <c r="D97" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.5">
-      <c r="A98" s="40"/>
-      <c r="B98" s="40"/>
-      <c r="C98" s="43"/>
+      <c r="A98" s="49"/>
+      <c r="B98" s="49"/>
+      <c r="C98" s="46"/>
       <c r="D98" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.5">
-      <c r="A99" s="40"/>
-      <c r="B99" s="40"/>
-      <c r="C99" s="42" t="s">
+      <c r="A99" s="49"/>
+      <c r="B99" s="49"/>
+      <c r="C99" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D99" s="28" t="s">
@@ -10607,29 +10629,29 @@
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.5">
-      <c r="A100" s="40"/>
-      <c r="B100" s="40"/>
-      <c r="C100" s="43"/>
+      <c r="A100" s="49"/>
+      <c r="B100" s="49"/>
+      <c r="C100" s="46"/>
       <c r="D100" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.5">
-      <c r="A101" s="40"/>
-      <c r="B101" s="40"/>
-      <c r="C101" s="43"/>
+      <c r="A101" s="49"/>
+      <c r="B101" s="49"/>
+      <c r="C101" s="46"/>
       <c r="D101" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.5">
-      <c r="A102" s="39">
+      <c r="A102" s="51">
         <v>8</v>
       </c>
-      <c r="B102" s="41" t="s">
+      <c r="B102" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="C102" s="42" t="s">
+      <c r="C102" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D102" s="28" t="s">
@@ -10637,49 +10659,49 @@
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.5">
-      <c r="A103" s="40"/>
-      <c r="B103" s="40"/>
-      <c r="C103" s="43"/>
+      <c r="A103" s="49"/>
+      <c r="B103" s="49"/>
+      <c r="C103" s="46"/>
       <c r="D103" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.5">
-      <c r="A104" s="40"/>
-      <c r="B104" s="40"/>
-      <c r="C104" s="43"/>
+      <c r="A104" s="49"/>
+      <c r="B104" s="49"/>
+      <c r="C104" s="46"/>
       <c r="D104" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.5">
-      <c r="A105" s="40"/>
-      <c r="B105" s="40"/>
-      <c r="C105" s="43"/>
+      <c r="A105" s="49"/>
+      <c r="B105" s="49"/>
+      <c r="C105" s="46"/>
       <c r="D105" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.5">
-      <c r="A106" s="40"/>
-      <c r="B106" s="40"/>
-      <c r="C106" s="43"/>
+      <c r="A106" s="49"/>
+      <c r="B106" s="49"/>
+      <c r="C106" s="46"/>
       <c r="D106" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.5">
-      <c r="A107" s="40"/>
-      <c r="B107" s="40"/>
-      <c r="C107" s="43"/>
+      <c r="A107" s="49"/>
+      <c r="B107" s="49"/>
+      <c r="C107" s="46"/>
       <c r="D107" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.5">
-      <c r="A108" s="40"/>
-      <c r="B108" s="40"/>
-      <c r="C108" s="42" t="s">
+      <c r="A108" s="49"/>
+      <c r="B108" s="49"/>
+      <c r="C108" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D108" s="28" t="s">
@@ -10687,25 +10709,25 @@
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.5">
-      <c r="A109" s="40"/>
-      <c r="B109" s="40"/>
-      <c r="C109" s="43"/>
+      <c r="A109" s="49"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="46"/>
       <c r="D109" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.5">
-      <c r="A110" s="40"/>
-      <c r="B110" s="40"/>
-      <c r="C110" s="43"/>
+      <c r="A110" s="49"/>
+      <c r="B110" s="49"/>
+      <c r="C110" s="46"/>
       <c r="D110" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.5">
-      <c r="A111" s="40"/>
-      <c r="B111" s="40"/>
-      <c r="C111" s="42" t="s">
+      <c r="A111" s="49"/>
+      <c r="B111" s="49"/>
+      <c r="C111" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D111" s="28" t="s">
@@ -10713,29 +10735,29 @@
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.5">
-      <c r="A112" s="40"/>
-      <c r="B112" s="40"/>
-      <c r="C112" s="43"/>
+      <c r="A112" s="49"/>
+      <c r="B112" s="49"/>
+      <c r="C112" s="46"/>
       <c r="D112" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.5">
-      <c r="A113" s="40"/>
-      <c r="B113" s="40"/>
-      <c r="C113" s="43"/>
+      <c r="A113" s="49"/>
+      <c r="B113" s="49"/>
+      <c r="C113" s="46"/>
       <c r="D113" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.5">
-      <c r="A114" s="39">
+      <c r="A114" s="51">
         <v>9</v>
       </c>
-      <c r="B114" s="41" t="s">
+      <c r="B114" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="C114" s="42" t="s">
+      <c r="C114" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D114" s="28" t="s">
@@ -10743,49 +10765,49 @@
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.5">
-      <c r="A115" s="40"/>
-      <c r="B115" s="47"/>
-      <c r="C115" s="43"/>
+      <c r="A115" s="49"/>
+      <c r="B115" s="43"/>
+      <c r="C115" s="46"/>
       <c r="D115" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.5">
-      <c r="A116" s="40"/>
-      <c r="B116" s="47"/>
-      <c r="C116" s="43"/>
+      <c r="A116" s="49"/>
+      <c r="B116" s="43"/>
+      <c r="C116" s="46"/>
       <c r="D116" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.5">
-      <c r="A117" s="40"/>
-      <c r="B117" s="47"/>
-      <c r="C117" s="43"/>
+      <c r="A117" s="49"/>
+      <c r="B117" s="43"/>
+      <c r="C117" s="46"/>
       <c r="D117" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.5">
-      <c r="A118" s="40"/>
-      <c r="B118" s="47"/>
-      <c r="C118" s="43"/>
+      <c r="A118" s="49"/>
+      <c r="B118" s="43"/>
+      <c r="C118" s="46"/>
       <c r="D118" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.5">
-      <c r="A119" s="40"/>
-      <c r="B119" s="47"/>
-      <c r="C119" s="43"/>
+      <c r="A119" s="49"/>
+      <c r="B119" s="43"/>
+      <c r="C119" s="46"/>
       <c r="D119" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.5">
-      <c r="A120" s="40"/>
-      <c r="B120" s="47"/>
-      <c r="C120" s="42" t="s">
+      <c r="A120" s="49"/>
+      <c r="B120" s="43"/>
+      <c r="C120" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D120" s="28" t="s">
@@ -10793,25 +10815,25 @@
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.5">
-      <c r="A121" s="40"/>
-      <c r="B121" s="47"/>
-      <c r="C121" s="43"/>
+      <c r="A121" s="49"/>
+      <c r="B121" s="43"/>
+      <c r="C121" s="46"/>
       <c r="D121" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.5">
-      <c r="A122" s="40"/>
-      <c r="B122" s="47"/>
-      <c r="C122" s="43"/>
+      <c r="A122" s="49"/>
+      <c r="B122" s="43"/>
+      <c r="C122" s="46"/>
       <c r="D122" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.5">
-      <c r="A123" s="40"/>
-      <c r="B123" s="47"/>
-      <c r="C123" s="42" t="s">
+      <c r="A123" s="49"/>
+      <c r="B123" s="43"/>
+      <c r="C123" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D123" s="28" t="s">
@@ -10819,28 +10841,28 @@
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.5">
-      <c r="A124" s="40"/>
-      <c r="B124" s="47"/>
-      <c r="C124" s="43"/>
+      <c r="A124" s="49"/>
+      <c r="B124" s="43"/>
+      <c r="C124" s="46"/>
       <c r="D124" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.5">
-      <c r="A125" s="40"/>
-      <c r="B125" s="47"/>
-      <c r="C125" s="43"/>
+      <c r="A125" s="49"/>
+      <c r="B125" s="43"/>
+      <c r="C125" s="46"/>
       <c r="D125" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15">
-      <c r="A126" s="48" t="s">
+      <c r="A126" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="B126" s="49"/>
-      <c r="C126" s="49"/>
-      <c r="D126" s="49"/>
+      <c r="B126" s="48"/>
+      <c r="C126" s="48"/>
+      <c r="D126" s="48"/>
     </row>
     <row r="127" spans="1:4" ht="15.5">
       <c r="A127" s="27" t="s">
@@ -10857,13 +10879,13 @@
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.5">
-      <c r="A128" s="50" t="s">
+      <c r="A128" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="B128" s="41" t="s">
+      <c r="B128" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="C128" s="42" t="s">
+      <c r="C128" s="45" t="s">
         <v>95</v>
       </c>
       <c r="D128" s="28" t="s">
@@ -10871,49 +10893,49 @@
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.5">
-      <c r="A129" s="47"/>
-      <c r="B129" s="40"/>
-      <c r="C129" s="43"/>
+      <c r="A129" s="43"/>
+      <c r="B129" s="49"/>
+      <c r="C129" s="46"/>
       <c r="D129" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.5">
-      <c r="A130" s="47"/>
-      <c r="B130" s="40"/>
-      <c r="C130" s="43"/>
+      <c r="A130" s="43"/>
+      <c r="B130" s="49"/>
+      <c r="C130" s="46"/>
       <c r="D130" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.5">
-      <c r="A131" s="47"/>
-      <c r="B131" s="40"/>
-      <c r="C131" s="43"/>
+      <c r="A131" s="43"/>
+      <c r="B131" s="49"/>
+      <c r="C131" s="46"/>
       <c r="D131" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.5">
-      <c r="A132" s="47"/>
-      <c r="B132" s="40"/>
-      <c r="C132" s="43"/>
+      <c r="A132" s="43"/>
+      <c r="B132" s="49"/>
+      <c r="C132" s="46"/>
       <c r="D132" s="28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.5">
-      <c r="A133" s="47"/>
-      <c r="B133" s="40"/>
-      <c r="C133" s="43"/>
+      <c r="A133" s="43"/>
+      <c r="B133" s="49"/>
+      <c r="C133" s="46"/>
       <c r="D133" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.5">
-      <c r="A134" s="47"/>
-      <c r="B134" s="40"/>
-      <c r="C134" s="42" t="s">
+      <c r="A134" s="43"/>
+      <c r="B134" s="49"/>
+      <c r="C134" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D134" s="28" t="s">
@@ -10921,25 +10943,25 @@
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.5">
-      <c r="A135" s="47"/>
-      <c r="B135" s="40"/>
-      <c r="C135" s="43"/>
+      <c r="A135" s="43"/>
+      <c r="B135" s="49"/>
+      <c r="C135" s="46"/>
       <c r="D135" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.5">
-      <c r="A136" s="47"/>
-      <c r="B136" s="40"/>
-      <c r="C136" s="43"/>
+      <c r="A136" s="43"/>
+      <c r="B136" s="49"/>
+      <c r="C136" s="46"/>
       <c r="D136" s="28" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.5">
-      <c r="A137" s="47"/>
-      <c r="B137" s="40"/>
-      <c r="C137" s="42" t="s">
+      <c r="A137" s="43"/>
+      <c r="B137" s="49"/>
+      <c r="C137" s="45" t="s">
         <v>96</v>
       </c>
       <c r="D137" s="28" t="s">
@@ -10947,69 +10969,23 @@
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.5">
-      <c r="A138" s="47"/>
-      <c r="B138" s="40"/>
-      <c r="C138" s="43"/>
+      <c r="A138" s="43"/>
+      <c r="B138" s="49"/>
+      <c r="C138" s="46"/>
       <c r="D138" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.5">
-      <c r="A139" s="47"/>
-      <c r="B139" s="40"/>
-      <c r="C139" s="43"/>
+      <c r="A139" s="43"/>
+      <c r="B139" s="49"/>
+      <c r="C139" s="46"/>
       <c r="D139" s="28" t="s">
         <v>104</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="A126:D126"/>
-    <mergeCell ref="A128:A139"/>
-    <mergeCell ref="B128:B139"/>
-    <mergeCell ref="C128:C133"/>
-    <mergeCell ref="C134:C136"/>
-    <mergeCell ref="C137:C139"/>
-    <mergeCell ref="A102:A113"/>
-    <mergeCell ref="B102:B113"/>
-    <mergeCell ref="C102:C107"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="C111:C113"/>
-    <mergeCell ref="A114:A125"/>
-    <mergeCell ref="B114:B125"/>
-    <mergeCell ref="C114:C119"/>
-    <mergeCell ref="C120:C122"/>
-    <mergeCell ref="C123:C125"/>
-    <mergeCell ref="A78:A89"/>
-    <mergeCell ref="B78:B89"/>
-    <mergeCell ref="C78:C83"/>
-    <mergeCell ref="C84:C86"/>
-    <mergeCell ref="C87:C89"/>
-    <mergeCell ref="A90:A101"/>
-    <mergeCell ref="B90:B101"/>
-    <mergeCell ref="C90:C95"/>
-    <mergeCell ref="C96:C98"/>
-    <mergeCell ref="C99:C101"/>
-    <mergeCell ref="A40:A55"/>
-    <mergeCell ref="B40:B55"/>
-    <mergeCell ref="C40:C45"/>
-    <mergeCell ref="C46:C50"/>
-    <mergeCell ref="C51:C55"/>
-    <mergeCell ref="A56:A77"/>
-    <mergeCell ref="B56:B77"/>
-    <mergeCell ref="C56:C61"/>
-    <mergeCell ref="C62:C69"/>
-    <mergeCell ref="C70:C77"/>
-    <mergeCell ref="A16:A27"/>
-    <mergeCell ref="B16:B27"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="A28:A39"/>
-    <mergeCell ref="B28:B39"/>
-    <mergeCell ref="C28:C33"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="C37:C39"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:A15"/>
@@ -11017,6 +10993,52 @@
     <mergeCell ref="C4:C9"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="C13:C15"/>
+    <mergeCell ref="A28:A39"/>
+    <mergeCell ref="B28:B39"/>
+    <mergeCell ref="C28:C33"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="A16:A27"/>
+    <mergeCell ref="B16:B27"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="A56:A77"/>
+    <mergeCell ref="B56:B77"/>
+    <mergeCell ref="C56:C61"/>
+    <mergeCell ref="C62:C69"/>
+    <mergeCell ref="C70:C77"/>
+    <mergeCell ref="A40:A55"/>
+    <mergeCell ref="B40:B55"/>
+    <mergeCell ref="C40:C45"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="C51:C55"/>
+    <mergeCell ref="A90:A101"/>
+    <mergeCell ref="B90:B101"/>
+    <mergeCell ref="C90:C95"/>
+    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="C99:C101"/>
+    <mergeCell ref="A78:A89"/>
+    <mergeCell ref="B78:B89"/>
+    <mergeCell ref="C78:C83"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="C87:C89"/>
+    <mergeCell ref="A114:A125"/>
+    <mergeCell ref="B114:B125"/>
+    <mergeCell ref="C114:C119"/>
+    <mergeCell ref="C120:C122"/>
+    <mergeCell ref="C123:C125"/>
+    <mergeCell ref="A102:A113"/>
+    <mergeCell ref="B102:B113"/>
+    <mergeCell ref="C102:C107"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="C111:C113"/>
+    <mergeCell ref="A126:D126"/>
+    <mergeCell ref="A128:A139"/>
+    <mergeCell ref="B128:B139"/>
+    <mergeCell ref="C128:C133"/>
+    <mergeCell ref="C134:C136"/>
+    <mergeCell ref="C137:C139"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11028,7 +11050,7 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="35" t="s">
         <v>175</v>
       </c>
     </row>
@@ -11043,7 +11065,7 @@
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="105" t="s">
+      <c r="A5" s="36" t="s">
         <v>178</v>
       </c>
     </row>
@@ -11058,7 +11080,7 @@
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="105" t="s">
+      <c r="A9" s="36" t="s">
         <v>181</v>
       </c>
     </row>
@@ -11073,7 +11095,7 @@
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="105" t="s">
+      <c r="A13" s="36" t="s">
         <v>184</v>
       </c>
     </row>
@@ -11088,7 +11110,7 @@
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="105" t="s">
+      <c r="A17" s="36" t="s">
         <v>187</v>
       </c>
     </row>
@@ -11098,7 +11120,7 @@
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="105" t="s">
+      <c r="A20" s="36" t="s">
         <v>189</v>
       </c>
     </row>
@@ -11108,7 +11130,7 @@
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="36" t="s">
         <v>191</v>
       </c>
     </row>
@@ -11123,7 +11145,7 @@
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="106" t="s">
+      <c r="A27" s="37" t="s">
         <v>194</v>
       </c>
     </row>
@@ -11135,4 +11157,76 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BDC0CA6-547E-440D-A77C-86508EAED0F1}">
+  <dimension ref="B2:H6"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="2" spans="2:8">
+      <c r="B2" s="107" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+    </row>
+    <row r="3" spans="2:8" ht="29" customHeight="1">
+      <c r="B3" s="108" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="107" t="s">
+        <v>198</v>
+      </c>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+    </row>
+    <row r="5" spans="2:8" ht="16" customHeight="1">
+      <c r="B5" s="108" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+    </row>
+    <row r="6" spans="2:8" ht="29.5" customHeight="1">
+      <c r="B6" s="108" t="s">
+        <v>200</v>
+      </c>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="108"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B6:H6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>